--- a/Data/National Accounts/PSA-Annual-1946-to-latest.xlsx
+++ b/Data/National Accounts/PSA-Annual-1946-to-latest.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Consol\QNAP\Pub tables\81 and 46 series\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP 1981 and 1946 series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A076E4-6849-498F-B811-52BBA06DFC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2B78A3-308B-4DA7-A647-60B1AAA2AB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Option 1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -19,9 +19,6 @@
     <sheet name="Constant_2018based" sheetId="7" r:id="rId4"/>
     <sheet name="Bkcast_cons" sheetId="4" state="hidden" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="114">
   <si>
     <t>Old</t>
   </si>
@@ -306,6 +303,84 @@
   <si>
     <t>1947 to 2025</t>
   </si>
+  <si>
+    <t>As of April 2026</t>
+  </si>
+  <si>
+    <t>2000 - 2001</t>
+  </si>
+  <si>
+    <t>2001 - 2002</t>
+  </si>
+  <si>
+    <t>2002 - 2003</t>
+  </si>
+  <si>
+    <t>2003 - 2004</t>
+  </si>
+  <si>
+    <t>2004 - 2005</t>
+  </si>
+  <si>
+    <t>2005 - 2006</t>
+  </si>
+  <si>
+    <t>2006 - 2007</t>
+  </si>
+  <si>
+    <t>2007 - 2008</t>
+  </si>
+  <si>
+    <t>2008 - 2009</t>
+  </si>
+  <si>
+    <t>2009 - 2010</t>
+  </si>
+  <si>
+    <t>2010 - 2011</t>
+  </si>
+  <si>
+    <t>2011 - 2012</t>
+  </si>
+  <si>
+    <t>2012 - 2013</t>
+  </si>
+  <si>
+    <t>2013 - 2014</t>
+  </si>
+  <si>
+    <t>2014 - 2015</t>
+  </si>
+  <si>
+    <t>2015 - 2016</t>
+  </si>
+  <si>
+    <t>2016 - 2017</t>
+  </si>
+  <si>
+    <t>2017 - 2018</t>
+  </si>
+  <si>
+    <t>2018 - 2019</t>
+  </si>
+  <si>
+    <t>2019 - 2020</t>
+  </si>
+  <si>
+    <t>2020 - 2021</t>
+  </si>
+  <si>
+    <t>2021 - 2022</t>
+  </si>
+  <si>
+    <t>2022 - 2023</t>
+  </si>
+  <si>
+    <t>2023 - 2024</t>
+  </si>
+  <si>
+    <t>2024 - 2025</t>
+  </si>
 </sst>
 </file>
 
@@ -533,2053 +608,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Prod_GR"/>
-      <sheetName val="Exp_GR"/>
-      <sheetName val="Prod_ConGrow"/>
-      <sheetName val="Exp_ConGrow"/>
-      <sheetName val="Prod_Share to GDP"/>
-      <sheetName val="Exp_Share to GDP"/>
-      <sheetName val="Prod_ConRev"/>
-      <sheetName val="Exp_ConRev"/>
-      <sheetName val="3Q"/>
-      <sheetName val="Sem"/>
-      <sheetName val="Annual"/>
-      <sheetName val="Qtr"/>
-      <sheetName val="Summary"/>
-      <sheetName val="Prod_Rev"/>
-      <sheetName val="Exp_Rev"/>
-      <sheetName val="Prod_Q_Rev_3yr"/>
-      <sheetName val="Exp_Q_Rev_3yr"/>
-      <sheetName val="Prod_A_Rev_3yr"/>
-      <sheetName val="Exp_A_Rev_3yr"/>
-      <sheetName val="Prod_Q"/>
-      <sheetName val="Exp_Q"/>
-      <sheetName val="Prod_S"/>
-      <sheetName val="Exp_S"/>
-      <sheetName val="Prod_A"/>
-      <sheetName val="Exp_A"/>
-      <sheetName val="Prod_3Q"/>
-      <sheetName val="Exp_3Q"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>As of January 2026</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="B88">
-            <v>515479.83105914737</v>
-          </cell>
-          <cell r="C88">
-            <v>535358.11662950239</v>
-          </cell>
-          <cell r="D88">
-            <v>585081.26403037924</v>
-          </cell>
-          <cell r="E88">
-            <v>620436.58457756066</v>
-          </cell>
-          <cell r="F88">
-            <v>744516.25225188024</v>
-          </cell>
-          <cell r="G88">
-            <v>799871.41640274995</v>
-          </cell>
-          <cell r="H88">
-            <v>875217.54801529867</v>
-          </cell>
-          <cell r="I88">
-            <v>979429.73898867343</v>
-          </cell>
-          <cell r="J88">
-            <v>1168573.1402468833</v>
-          </cell>
-          <cell r="K88">
-            <v>1219985.1777794692</v>
-          </cell>
-          <cell r="L88">
-            <v>1292317.8004069938</v>
-          </cell>
-          <cell r="M88">
-            <v>1429964.5926411448</v>
-          </cell>
-          <cell r="N88">
-            <v>1448473.3675359092</v>
-          </cell>
-          <cell r="O88">
-            <v>1503121.5657752962</v>
-          </cell>
-          <cell r="P88">
-            <v>1620699.915263247</v>
-          </cell>
-          <cell r="Q88">
-            <v>1533369.1559169192</v>
-          </cell>
-          <cell r="R88">
-            <v>1544278.5250839123</v>
-          </cell>
-          <cell r="S88">
-            <v>1685956.1855432384</v>
-          </cell>
-          <cell r="T88">
-            <v>1762616.4965786883</v>
-          </cell>
-          <cell r="U88">
-            <v>1721538.720258696</v>
-          </cell>
-          <cell r="V88">
-            <v>1828423.603228105</v>
-          </cell>
-          <cell r="W88">
-            <v>1954486.610016682</v>
-          </cell>
-          <cell r="X88">
-            <v>2104089.8599160332</v>
-          </cell>
-          <cell r="Y88">
-            <v>2285564.0565247671</v>
-          </cell>
-          <cell r="Z88">
-            <v>2401998.5929831276</v>
-          </cell>
-          <cell r="AA88">
-            <v>2407377.1641075336</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="B89">
-            <v>1293230.8123216361</v>
-          </cell>
-          <cell r="C89">
-            <v>1404419.2585960752</v>
-          </cell>
-          <cell r="D89">
-            <v>1513274.1419064312</v>
-          </cell>
-          <cell r="E89">
-            <v>1629557.8179376805</v>
-          </cell>
-          <cell r="F89">
-            <v>1789827.1716504705</v>
-          </cell>
-          <cell r="G89">
-            <v>2000850.6834146297</v>
-          </cell>
-          <cell r="H89">
-            <v>2191938.9158876012</v>
-          </cell>
-          <cell r="I89">
-            <v>2375482.7850285335</v>
-          </cell>
-          <cell r="J89">
-            <v>2637671.450985474</v>
-          </cell>
-          <cell r="K89">
-            <v>2644874.1847134624</v>
-          </cell>
-          <cell r="L89">
-            <v>3039740.6458881143</v>
-          </cell>
-          <cell r="M89">
-            <v>3179203.2325789281</v>
-          </cell>
-          <cell r="N89">
-            <v>3472968.8558059549</v>
-          </cell>
-          <cell r="O89">
-            <v>3708623.5049130186</v>
-          </cell>
-          <cell r="P89">
-            <v>4100382.6683558412</v>
-          </cell>
-          <cell r="Q89">
-            <v>4250451.2383206487</v>
-          </cell>
-          <cell r="R89">
-            <v>4582980.5174834859</v>
-          </cell>
-          <cell r="S89">
-            <v>4987947.8624290526</v>
-          </cell>
-          <cell r="T89">
-            <v>5582525.2893169122</v>
-          </cell>
-          <cell r="U89">
-            <v>5919281.4913050616</v>
-          </cell>
-          <cell r="V89">
-            <v>5098232.0991026126</v>
-          </cell>
-          <cell r="W89">
-            <v>5607689.4737621192</v>
-          </cell>
-          <cell r="X89">
-            <v>6436935.4825338945</v>
-          </cell>
-          <cell r="Y89">
-            <v>6855846.7681841524</v>
-          </cell>
-          <cell r="Z89">
-            <v>7324051.7478946894</v>
-          </cell>
-          <cell r="AA89">
-            <v>7549475.326033894</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="B94">
-            <v>1888845.5620071718</v>
-          </cell>
-          <cell r="C94">
-            <v>2084621.56495832</v>
-          </cell>
-          <cell r="D94">
-            <v>2252204.3661971181</v>
-          </cell>
-          <cell r="E94">
-            <v>2467814.5379699469</v>
-          </cell>
-          <cell r="F94">
-            <v>2789560.7532976717</v>
-          </cell>
-          <cell r="G94">
-            <v>3116560.2013509646</v>
-          </cell>
-          <cell r="H94">
-            <v>3483260.64902006</v>
-          </cell>
-          <cell r="I94">
-            <v>3843332.3637472363</v>
-          </cell>
-          <cell r="J94">
-            <v>4243956.0293361945</v>
-          </cell>
-          <cell r="K94">
-            <v>4525562.0937777292</v>
-          </cell>
-          <cell r="L94">
-            <v>5067392.3117788061</v>
-          </cell>
-          <cell r="M94">
-            <v>5535493.5015616529</v>
-          </cell>
-          <cell r="N94">
-            <v>6139146.6072256053</v>
-          </cell>
-          <cell r="O94">
-            <v>6838846.913572249</v>
-          </cell>
-          <cell r="P94">
-            <v>7485745.6680728551</v>
-          </cell>
-          <cell r="Q94">
-            <v>8160337.0535270972</v>
-          </cell>
-          <cell r="R94">
-            <v>9005122.4276059344</v>
-          </cell>
-          <cell r="S94">
-            <v>9882747.0352535639</v>
-          </cell>
-          <cell r="T94">
-            <v>10920048.472266145</v>
-          </cell>
-          <cell r="U94">
-            <v>11877042.96011826</v>
-          </cell>
-          <cell r="V94">
-            <v>11024917.867682004</v>
-          </cell>
-          <cell r="W94">
-            <v>11848438.402404422</v>
-          </cell>
-          <cell r="X94">
-            <v>13487250.995206343</v>
-          </cell>
-          <cell r="Y94">
-            <v>15172152.370130764</v>
-          </cell>
-          <cell r="Z94">
-            <v>16720319.15398364</v>
-          </cell>
-          <cell r="AA94">
-            <v>18057411.945117269</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="B107">
-            <v>3697556.2053879555</v>
-          </cell>
-          <cell r="C107">
-            <v>4024398.9401838975</v>
-          </cell>
-          <cell r="D107">
-            <v>4350559.7721339278</v>
-          </cell>
-          <cell r="E107">
-            <v>4717808.9404851878</v>
-          </cell>
-          <cell r="F107">
-            <v>5323904.1772000222</v>
-          </cell>
-          <cell r="G107">
-            <v>5917282.301168344</v>
-          </cell>
-          <cell r="H107">
-            <v>6550417.11292296</v>
-          </cell>
-          <cell r="I107">
-            <v>7198244.8877644427</v>
-          </cell>
-          <cell r="J107">
-            <v>8050200.6205685521</v>
-          </cell>
-          <cell r="K107">
-            <v>8390421.4562706612</v>
-          </cell>
-          <cell r="L107">
-            <v>9399450.7580739148</v>
-          </cell>
-          <cell r="M107">
-            <v>10144661.326781726</v>
-          </cell>
-          <cell r="N107">
-            <v>11060588.830567468</v>
-          </cell>
-          <cell r="O107">
-            <v>12050591.984260563</v>
-          </cell>
-          <cell r="P107">
-            <v>13206828.251691943</v>
-          </cell>
-          <cell r="Q107">
-            <v>13944157.447764665</v>
-          </cell>
-          <cell r="R107">
-            <v>15132381.470173333</v>
-          </cell>
-          <cell r="S107">
-            <v>16556651.083225854</v>
-          </cell>
-          <cell r="T107">
-            <v>18265190.258161746</v>
-          </cell>
-          <cell r="U107">
-            <v>19517863.171682019</v>
-          </cell>
-          <cell r="V107">
-            <v>17951573.570012722</v>
-          </cell>
-          <cell r="W107">
-            <v>19410614.486183222</v>
-          </cell>
-          <cell r="X107">
-            <v>22028276.337656271</v>
-          </cell>
-          <cell r="Y107">
-            <v>24313563.194839686</v>
-          </cell>
-          <cell r="Z107">
-            <v>26446369.494861454</v>
-          </cell>
-          <cell r="AA107">
-            <v>28014264.435258694</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="B127">
-            <v>1064005.0869465019</v>
-          </cell>
-          <cell r="C127">
-            <v>1105117.4866392382</v>
-          </cell>
-          <cell r="D127">
-            <v>1144990.5954578116</v>
-          </cell>
-          <cell r="E127">
-            <v>1197371.0373716741</v>
-          </cell>
-          <cell r="F127">
-            <v>1257109.2132941873</v>
-          </cell>
-          <cell r="G127">
-            <v>1301069.2243305743</v>
-          </cell>
-          <cell r="H127">
-            <v>1360678.1688071573</v>
-          </cell>
-          <cell r="I127">
-            <v>1433746.8087559578</v>
-          </cell>
-          <cell r="J127">
-            <v>1482351.7473987523</v>
-          </cell>
-          <cell r="K127">
-            <v>1480206.8239089095</v>
-          </cell>
-          <cell r="L127">
-            <v>1499800.7696724271</v>
-          </cell>
-          <cell r="M127">
-            <v>1550555.2016332422</v>
-          </cell>
-          <cell r="N127">
-            <v>1598311.5075543907</v>
-          </cell>
-          <cell r="O127">
-            <v>1645191.6850298091</v>
-          </cell>
-          <cell r="P127">
-            <v>1676006.3550526681</v>
-          </cell>
-          <cell r="Q127">
-            <v>1688343.7557025508</v>
-          </cell>
-          <cell r="R127">
-            <v>1672084.9828823139</v>
-          </cell>
-          <cell r="S127">
-            <v>1743134.2940204137</v>
-          </cell>
-          <cell r="T127">
-            <v>1762616.4965786885</v>
-          </cell>
-          <cell r="U127">
-            <v>1783855.1472581751</v>
-          </cell>
-          <cell r="V127">
-            <v>1780390.5640921537</v>
-          </cell>
-          <cell r="W127">
-            <v>1775210.3171187984</v>
-          </cell>
-          <cell r="X127">
-            <v>1783734.6554432954</v>
-          </cell>
-          <cell r="Y127">
-            <v>1805216.771038763</v>
-          </cell>
-          <cell r="Z127">
-            <v>1778234.5329187952</v>
-          </cell>
-          <cell r="AA127">
-            <v>1833110.7044894486</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="B128">
-            <v>2233331.908558073</v>
-          </cell>
-          <cell r="C128">
-            <v>2263212.7783727339</v>
-          </cell>
-          <cell r="D128">
-            <v>2346382.7963735494</v>
-          </cell>
-          <cell r="E128">
-            <v>2462870.600499433</v>
-          </cell>
-          <cell r="F128">
-            <v>2571406.3345832815</v>
-          </cell>
-          <cell r="G128">
-            <v>2701284.7496357504</v>
-          </cell>
-          <cell r="H128">
-            <v>2802098.6329476382</v>
-          </cell>
-          <cell r="I128">
-            <v>2940674.679845708</v>
-          </cell>
-          <cell r="J128">
-            <v>3101573.6524675926</v>
-          </cell>
-          <cell r="K128">
-            <v>3057652.2915348206</v>
-          </cell>
-          <cell r="L128">
-            <v>3358023.2875841749</v>
-          </cell>
-          <cell r="M128">
-            <v>3411809.2007066575</v>
-          </cell>
-          <cell r="N128">
-            <v>3674109.760798207</v>
-          </cell>
-          <cell r="O128">
-            <v>3924518.7466281406</v>
-          </cell>
-          <cell r="P128">
-            <v>4218871.831168456</v>
-          </cell>
-          <cell r="Q128">
-            <v>4493389.9589908756</v>
-          </cell>
-          <cell r="R128">
-            <v>4861341.7522844896</v>
-          </cell>
-          <cell r="S128">
-            <v>5202581.5831372812</v>
-          </cell>
-          <cell r="T128">
-            <v>5582525.2893169122</v>
-          </cell>
-          <cell r="U128">
-            <v>5887868.6968866978</v>
-          </cell>
-          <cell r="V128">
-            <v>5115315.7129913447</v>
-          </cell>
-          <cell r="W128">
-            <v>5551621.8662187792</v>
-          </cell>
-          <cell r="X128">
-            <v>5913747.6649654768</v>
-          </cell>
-          <cell r="Y128">
-            <v>6128235.4957260517</v>
-          </cell>
-          <cell r="Z128">
-            <v>6473862.2736754334</v>
-          </cell>
-          <cell r="AA128">
-            <v>6572519.1983347684</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="B133">
-            <v>3688046.2446433334</v>
-          </cell>
-          <cell r="C133">
-            <v>3830053.4704007208</v>
-          </cell>
-          <cell r="D133">
-            <v>3974520.639199873</v>
-          </cell>
-          <cell r="E133">
-            <v>4185435.7878863006</v>
-          </cell>
-          <cell r="F133">
-            <v>4532562.3563551698</v>
-          </cell>
-          <cell r="G133">
-            <v>4771970.6335892519</v>
-          </cell>
-          <cell r="H133">
-            <v>5078027.4752690587</v>
-          </cell>
-          <cell r="I133">
-            <v>5468817.7608404998</v>
-          </cell>
-          <cell r="J133">
-            <v>5686952.1291571362</v>
-          </cell>
-          <cell r="K133">
-            <v>5881773.9015875971</v>
-          </cell>
-          <cell r="L133">
-            <v>6326036.9392845146</v>
-          </cell>
-          <cell r="M133">
-            <v>6652995.9905493334</v>
-          </cell>
-          <cell r="N133">
-            <v>7144044.9218433676</v>
-          </cell>
-          <cell r="O133">
-            <v>7684933.195281975</v>
-          </cell>
-          <cell r="P133">
-            <v>8201168.5590072311</v>
-          </cell>
-          <cell r="Q133">
-            <v>8809173.7357357219</v>
-          </cell>
-          <cell r="R133">
-            <v>9529249.1598030627</v>
-          </cell>
-          <cell r="S133">
-            <v>10230262.208913909</v>
-          </cell>
-          <cell r="T133">
-            <v>10920048.472266145</v>
-          </cell>
-          <cell r="U133">
-            <v>11711026.767278373</v>
-          </cell>
-          <cell r="V133">
-            <v>10642137.002289824</v>
-          </cell>
-          <cell r="W133">
-            <v>11213252.036594167</v>
-          </cell>
-          <cell r="X133">
-            <v>12248122.370699735</v>
-          </cell>
-          <cell r="Y133">
-            <v>13112940.310321592</v>
-          </cell>
-          <cell r="Z133">
-            <v>13992259.830376996</v>
-          </cell>
-          <cell r="AA133">
-            <v>14818232.355490401</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="B146">
-            <v>6985383.2401479082</v>
-          </cell>
-          <cell r="C146">
-            <v>7198383.7354126927</v>
-          </cell>
-          <cell r="D146">
-            <v>7465894.0310312342</v>
-          </cell>
-          <cell r="E146">
-            <v>7845677.4257574081</v>
-          </cell>
-          <cell r="F146">
-            <v>8361077.9042326389</v>
-          </cell>
-          <cell r="G146">
-            <v>8774324.6075555757</v>
-          </cell>
-          <cell r="H146">
-            <v>9240804.2770238537</v>
-          </cell>
-          <cell r="I146">
-            <v>9843239.2494421657</v>
-          </cell>
-          <cell r="J146">
-            <v>10270877.52902348</v>
-          </cell>
-          <cell r="K146">
-            <v>10419633.017031327</v>
-          </cell>
-          <cell r="L146">
-            <v>11183860.996541116</v>
-          </cell>
-          <cell r="M146">
-            <v>11615360.392889233</v>
-          </cell>
-          <cell r="N146">
-            <v>12416466.190195967</v>
-          </cell>
-          <cell r="O146">
-            <v>13254643.626939924</v>
-          </cell>
-          <cell r="P146">
-            <v>14096046.745228356</v>
-          </cell>
-          <cell r="Q146">
-            <v>14990907.450429149</v>
-          </cell>
-          <cell r="R146">
-            <v>16062675.894969866</v>
-          </cell>
-          <cell r="S146">
-            <v>17175978.086071603</v>
-          </cell>
-          <cell r="T146">
-            <v>18265190.258161746</v>
-          </cell>
-          <cell r="U146">
-            <v>19382750.611423247</v>
-          </cell>
-          <cell r="V146">
-            <v>17537843.279373322</v>
-          </cell>
-          <cell r="W146">
-            <v>18540084.219931744</v>
-          </cell>
-          <cell r="X146">
-            <v>19945604.69110851</v>
-          </cell>
-          <cell r="Y146">
-            <v>21046392.577086408</v>
-          </cell>
-          <cell r="Z146">
-            <v>22244356.636971224</v>
-          </cell>
-          <cell r="AA146">
-            <v>23223862.258314617</v>
-          </cell>
-        </row>
-        <row r="242">
-          <cell r="B242">
-            <v>13.941095210615254</v>
-          </cell>
-          <cell r="C242">
-            <v>13.302809303618366</v>
-          </cell>
-          <cell r="D242">
-            <v>13.44841341516381</v>
-          </cell>
-          <cell r="E242">
-            <v>13.150947662449294</v>
-          </cell>
-          <cell r="F242">
-            <v>13.984403690816247</v>
-          </cell>
-          <cell r="G242">
-            <v>13.517547003711798</v>
-          </cell>
-          <cell r="H242">
-            <v>13.361249107154258</v>
-          </cell>
-          <cell r="I242">
-            <v>13.606507617620867</v>
-          </cell>
-          <cell r="J242">
-            <v>14.516074757952453</v>
-          </cell>
-          <cell r="K242">
-            <v>14.540213315121395</v>
-          </cell>
-          <cell r="L242">
-            <v>13.74886505253429</v>
-          </cell>
-          <cell r="M242">
-            <v>14.095735151513274</v>
-          </cell>
-          <cell r="N242">
-            <v>13.095807011041332</v>
-          </cell>
-          <cell r="O242">
-            <v>12.473425104248347</v>
-          </cell>
-          <cell r="P242">
-            <v>12.271681620873787</v>
-          </cell>
-          <cell r="Q242">
-            <v>10.996499155011534</v>
-          </cell>
-          <cell r="R242">
-            <v>10.205125532473266</v>
-          </cell>
-          <cell r="S242">
-            <v>10.182954131656141</v>
-          </cell>
-          <cell r="T242">
-            <v>9.6501403580565963</v>
-          </cell>
-          <cell r="U242">
-            <v>8.8203237471017513</v>
-          </cell>
-          <cell r="V242">
-            <v>10.185311031910887</v>
-          </cell>
-          <cell r="W242">
-            <v>10.069164020582223</v>
-          </cell>
-          <cell r="X242">
-            <v>9.5517680442350059</v>
-          </cell>
-          <cell r="Y242">
-            <v>9.4003665287935068</v>
-          </cell>
-          <cell r="Z242">
-            <v>9.0825267848195104</v>
-          </cell>
-          <cell r="AA242">
-            <v>8.5933977301849627</v>
-          </cell>
-        </row>
-        <row r="243">
-          <cell r="B243">
-            <v>34.975284768820643</v>
-          </cell>
-          <cell r="C243">
-            <v>34.897615258091172</v>
-          </cell>
-          <cell r="D243">
-            <v>34.783435262726613</v>
-          </cell>
-          <cell r="E243">
-            <v>34.540564030770057</v>
-          </cell>
-          <cell r="F243">
-            <v>33.618696206357839</v>
-          </cell>
-          <cell r="G243">
-            <v>33.813676305752217</v>
-          </cell>
-          <cell r="H243">
-            <v>33.462585330073786</v>
-          </cell>
-          <cell r="I243">
-            <v>33.000860933008447</v>
-          </cell>
-          <cell r="J243">
-            <v>32.765288410901569</v>
-          </cell>
-          <cell r="K243">
-            <v>31.522542681533483</v>
-          </cell>
-          <cell r="L243">
-            <v>32.339556045623688</v>
-          </cell>
-          <cell r="M243">
-            <v>31.338682782695642</v>
-          </cell>
-          <cell r="N243">
-            <v>31.399493363390608</v>
-          </cell>
-          <cell r="O243">
-            <v>30.775446631641834</v>
-          </cell>
-          <cell r="P243">
-            <v>31.047444475024015</v>
-          </cell>
-          <cell r="Q243">
-            <v>30.481950983722022</v>
-          </cell>
-          <cell r="R243">
-            <v>30.285917167213672</v>
-          </cell>
-          <cell r="S243">
-            <v>30.126550576900929</v>
-          </cell>
-          <cell r="T243">
-            <v>30.563740154978003</v>
-          </cell>
-          <cell r="U243">
-            <v>30.327507879516236</v>
-          </cell>
-          <cell r="V243">
-            <v>28.399917585046552</v>
-          </cell>
-          <cell r="W243">
-            <v>28.88980911837572</v>
-          </cell>
-          <cell r="X243">
-            <v>29.221239936645727</v>
-          </cell>
-          <cell r="Y243">
-            <v>28.197622509066207</v>
-          </cell>
-          <cell r="Z243">
-            <v>27.693977993152359</v>
-          </cell>
-          <cell r="AA243">
-            <v>26.948683030678254</v>
-          </cell>
-        </row>
-        <row r="248">
-          <cell r="B248">
-            <v>51.083620020564105</v>
-          </cell>
-          <cell r="C248">
-            <v>51.799575438290468</v>
-          </cell>
-          <cell r="D248">
-            <v>51.768151322109588</v>
-          </cell>
-          <cell r="E248">
-            <v>52.308488306780653</v>
-          </cell>
-          <cell r="F248">
-            <v>52.396900102825917</v>
-          </cell>
-          <cell r="G248">
-            <v>52.668776690535992</v>
-          </cell>
-          <cell r="H248">
-            <v>53.176165562771956</v>
-          </cell>
-          <cell r="I248">
-            <v>53.392631449370697</v>
-          </cell>
-          <cell r="J248">
-            <v>52.718636831145972</v>
-          </cell>
-          <cell r="K248">
-            <v>53.937244003345121</v>
-          </cell>
-          <cell r="L248">
-            <v>53.91157890184202</v>
-          </cell>
-          <cell r="M248">
-            <v>54.565582065791084</v>
-          </cell>
-          <cell r="N248">
-            <v>55.504699625568065</v>
-          </cell>
-          <cell r="O248">
-            <v>56.751128264109816</v>
-          </cell>
-          <cell r="P248">
-            <v>56.680873904102199</v>
-          </cell>
-          <cell r="Q248">
-            <v>58.521549861266443</v>
-          </cell>
-          <cell r="R248">
-            <v>59.508957300313057</v>
-          </cell>
-          <cell r="S248">
-            <v>59.690495291442936</v>
-          </cell>
-          <cell r="T248">
-            <v>59.786119486965397</v>
-          </cell>
-          <cell r="U248">
-            <v>60.852168373382007</v>
-          </cell>
-          <cell r="V248">
-            <v>61.414771383042556</v>
-          </cell>
-          <cell r="W248">
-            <v>61.041026861042056</v>
-          </cell>
-          <cell r="X248">
-            <v>61.226992019119265</v>
-          </cell>
-          <cell r="Y248">
-            <v>62.402010962140274</v>
-          </cell>
-          <cell r="Z248">
-            <v>63.223495222028149</v>
-          </cell>
-          <cell r="AA248">
-            <v>64.457919239136785</v>
-          </cell>
-        </row>
-        <row r="261">
-          <cell r="B261">
-            <v>100</v>
-          </cell>
-          <cell r="C261">
-            <v>100</v>
-          </cell>
-          <cell r="D261">
-            <v>100</v>
-          </cell>
-          <cell r="E261">
-            <v>100</v>
-          </cell>
-          <cell r="F261">
-            <v>100</v>
-          </cell>
-          <cell r="G261">
-            <v>100</v>
-          </cell>
-          <cell r="H261">
-            <v>100</v>
-          </cell>
-          <cell r="I261">
-            <v>100</v>
-          </cell>
-          <cell r="J261">
-            <v>100</v>
-          </cell>
-          <cell r="K261">
-            <v>100</v>
-          </cell>
-          <cell r="L261">
-            <v>100</v>
-          </cell>
-          <cell r="M261">
-            <v>100</v>
-          </cell>
-          <cell r="N261">
-            <v>100</v>
-          </cell>
-          <cell r="O261">
-            <v>100</v>
-          </cell>
-          <cell r="P261">
-            <v>100</v>
-          </cell>
-          <cell r="Q261">
-            <v>100</v>
-          </cell>
-          <cell r="R261">
-            <v>100</v>
-          </cell>
-          <cell r="S261">
-            <v>100</v>
-          </cell>
-          <cell r="T261">
-            <v>100</v>
-          </cell>
-          <cell r="U261">
-            <v>100</v>
-          </cell>
-          <cell r="V261">
-            <v>100</v>
-          </cell>
-          <cell r="W261">
-            <v>100</v>
-          </cell>
-          <cell r="X261">
-            <v>100</v>
-          </cell>
-          <cell r="Y261">
-            <v>100</v>
-          </cell>
-          <cell r="Z261">
-            <v>100</v>
-          </cell>
-          <cell r="AA261">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="281">
-          <cell r="B281">
-            <v>15.23187848636881</v>
-          </cell>
-          <cell r="C281">
-            <v>15.352300283778639</v>
-          </cell>
-          <cell r="D281">
-            <v>15.336282442514907</v>
-          </cell>
-          <cell r="E281">
-            <v>15.261537944966964</v>
-          </cell>
-          <cell r="F281">
-            <v>15.035252962513354</v>
-          </cell>
-          <cell r="G281">
-            <v>14.828140996860578</v>
-          </cell>
-          <cell r="H281">
-            <v>14.724672528670688</v>
-          </cell>
-          <cell r="I281">
-            <v>14.565802703995139</v>
-          </cell>
-          <cell r="J281">
-            <v>14.432571542304128</v>
-          </cell>
-          <cell r="K281">
-            <v>14.205940089151406</v>
-          </cell>
-          <cell r="L281">
-            <v>13.410402455254742</v>
-          </cell>
-          <cell r="M281">
-            <v>13.349178580653176</v>
-          </cell>
-          <cell r="N281">
-            <v>12.872515279882263</v>
-          </cell>
-          <cell r="O281">
-            <v>12.412191012710249</v>
-          </cell>
-          <cell r="P281">
-            <v>11.889903498085461</v>
-          </cell>
-          <cell r="Q281">
-            <v>11.26245199822255</v>
-          </cell>
-          <cell r="R281">
-            <v>10.409753604042638</v>
-          </cell>
-          <cell r="S281">
-            <v>10.148675582172299</v>
-          </cell>
-          <cell r="T281">
-            <v>9.6501403580565963</v>
-          </cell>
-          <cell r="U281">
-            <v>9.2033126929201572</v>
-          </cell>
-          <cell r="V281">
-            <v>10.151707571626631</v>
-          </cell>
-          <cell r="W281">
-            <v>9.5749851837800009</v>
-          </cell>
-          <cell r="X281">
-            <v>8.9429961290592548</v>
-          </cell>
-          <cell r="Y281">
-            <v>8.5773215738840456</v>
-          </cell>
-          <cell r="Z281">
-            <v>7.9940928925913788</v>
-          </cell>
-          <cell r="AA281">
-            <v>7.8932207059278321</v>
-          </cell>
-        </row>
-        <row r="282">
-          <cell r="B282">
-            <v>31.971501516512134</v>
-          </cell>
-          <cell r="C282">
-            <v>31.440568627076409</v>
-          </cell>
-          <cell r="D282">
-            <v>31.428021702706282</v>
-          </cell>
-          <cell r="E282">
-            <v>31.39143335684199</v>
-          </cell>
-          <cell r="F282">
-            <v>30.754483620844571</v>
-          </cell>
-          <cell r="G282">
-            <v>30.786241339984993</v>
-          </cell>
-          <cell r="H282">
-            <v>30.323103367904015</v>
-          </cell>
-          <cell r="I282">
-            <v>29.875070648235653</v>
-          </cell>
-          <cell r="J282">
-            <v>30.197747404768048</v>
-          </cell>
-          <cell r="K282">
-            <v>29.345105403779193</v>
-          </cell>
-          <cell r="L282">
-            <v>30.025617169443773</v>
-          </cell>
-          <cell r="M282">
-            <v>29.373253048569385</v>
-          </cell>
-          <cell r="N282">
-            <v>29.590623487536909</v>
-          </cell>
-          <cell r="O282">
-            <v>29.608632695726328</v>
-          </cell>
-          <cell r="P282">
-            <v>29.929468221979217</v>
-          </cell>
-          <cell r="Q282">
-            <v>29.974102460770258</v>
-          </cell>
-          <cell r="R282">
-            <v>30.264831240272059</v>
-          </cell>
-          <cell r="S282">
-            <v>30.289870871203394</v>
-          </cell>
-          <cell r="T282">
-            <v>30.563740154978003</v>
-          </cell>
-          <cell r="U282">
-            <v>30.37684802804343</v>
-          </cell>
-          <cell r="V282">
-            <v>29.167301996634841</v>
-          </cell>
-          <cell r="W282">
-            <v>29.943886987581429</v>
-          </cell>
-          <cell r="X282">
-            <v>29.6493776776883</v>
-          </cell>
-          <cell r="Y282">
-            <v>29.117747724605188</v>
-          </cell>
-          <cell r="Z282">
-            <v>29.103391836990927</v>
-          </cell>
-          <cell r="AA282">
-            <v>28.300715553812211</v>
-          </cell>
-        </row>
-        <row r="287">
-          <cell r="B287">
-            <v>52.796619997119052</v>
-          </cell>
-          <cell r="C287">
-            <v>53.207131089144951</v>
-          </cell>
-          <cell r="D287">
-            <v>53.235695854778811</v>
-          </cell>
-          <cell r="E287">
-            <v>53.347028698191046</v>
-          </cell>
-          <cell r="F287">
-            <v>54.210263416642071</v>
-          </cell>
-          <cell r="G287">
-            <v>54.385617663154441</v>
-          </cell>
-          <cell r="H287">
-            <v>54.952224103425308</v>
-          </cell>
-          <cell r="I287">
-            <v>55.559126647769205</v>
-          </cell>
-          <cell r="J287">
-            <v>55.369681052927831</v>
-          </cell>
-          <cell r="K287">
-            <v>56.448954507069402</v>
-          </cell>
-          <cell r="L287">
-            <v>56.56398037530149</v>
-          </cell>
-          <cell r="M287">
-            <v>57.277568370777445</v>
-          </cell>
-          <cell r="N287">
-            <v>57.536861232580819</v>
-          </cell>
-          <cell r="O287">
-            <v>57.979176291563427</v>
-          </cell>
-          <cell r="P287">
-            <v>58.18062827993532</v>
-          </cell>
-          <cell r="Q287">
-            <v>58.763445541007187</v>
-          </cell>
-          <cell r="R287">
-            <v>59.325415155685299</v>
-          </cell>
-          <cell r="S287">
-            <v>59.561453546624307</v>
-          </cell>
-          <cell r="T287">
-            <v>59.786119486965397</v>
-          </cell>
-          <cell r="U287">
-            <v>60.419839279036417</v>
-          </cell>
-          <cell r="V287">
-            <v>60.680990431738536</v>
-          </cell>
-          <cell r="W287">
-            <v>60.481127828638584</v>
-          </cell>
-          <cell r="X287">
-            <v>61.407626193252426</v>
-          </cell>
-          <cell r="Y287">
-            <v>62.304930701510763</v>
-          </cell>
-          <cell r="Z287">
-            <v>62.902515270417695</v>
-          </cell>
-          <cell r="AA287">
-            <v>63.806063740259965</v>
-          </cell>
-        </row>
-        <row r="300">
-          <cell r="B300">
-            <v>100</v>
-          </cell>
-          <cell r="C300">
-            <v>100</v>
-          </cell>
-          <cell r="D300">
-            <v>100</v>
-          </cell>
-          <cell r="E300">
-            <v>100</v>
-          </cell>
-          <cell r="F300">
-            <v>100</v>
-          </cell>
-          <cell r="G300">
-            <v>100</v>
-          </cell>
-          <cell r="H300">
-            <v>100</v>
-          </cell>
-          <cell r="I300">
-            <v>100</v>
-          </cell>
-          <cell r="J300">
-            <v>100</v>
-          </cell>
-          <cell r="K300">
-            <v>100</v>
-          </cell>
-          <cell r="L300">
-            <v>100</v>
-          </cell>
-          <cell r="M300">
-            <v>100</v>
-          </cell>
-          <cell r="N300">
-            <v>100</v>
-          </cell>
-          <cell r="O300">
-            <v>100</v>
-          </cell>
-          <cell r="P300">
-            <v>100</v>
-          </cell>
-          <cell r="Q300">
-            <v>100</v>
-          </cell>
-          <cell r="R300">
-            <v>100</v>
-          </cell>
-          <cell r="S300">
-            <v>100</v>
-          </cell>
-          <cell r="T300">
-            <v>100</v>
-          </cell>
-          <cell r="U300">
-            <v>100</v>
-          </cell>
-          <cell r="V300">
-            <v>100</v>
-          </cell>
-          <cell r="W300">
-            <v>100</v>
-          </cell>
-          <cell r="X300">
-            <v>100</v>
-          </cell>
-          <cell r="Y300">
-            <v>100</v>
-          </cell>
-          <cell r="Z300">
-            <v>100</v>
-          </cell>
-          <cell r="AA300">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="394">
-          <cell r="B394" t="str">
-            <v>2000 - 2001</v>
-          </cell>
-          <cell r="C394" t="str">
-            <v>2001 - 2002</v>
-          </cell>
-          <cell r="D394" t="str">
-            <v>2002 - 2003</v>
-          </cell>
-          <cell r="E394" t="str">
-            <v>2003 - 2004</v>
-          </cell>
-          <cell r="F394" t="str">
-            <v>2004 - 2005</v>
-          </cell>
-          <cell r="G394" t="str">
-            <v>2005 - 2006</v>
-          </cell>
-          <cell r="H394" t="str">
-            <v>2006 - 2007</v>
-          </cell>
-          <cell r="I394" t="str">
-            <v>2007 - 2008</v>
-          </cell>
-          <cell r="J394" t="str">
-            <v>2008 - 2009</v>
-          </cell>
-          <cell r="K394" t="str">
-            <v>2009 - 2010</v>
-          </cell>
-          <cell r="L394" t="str">
-            <v>2010 - 2011</v>
-          </cell>
-          <cell r="M394" t="str">
-            <v>2011 - 2012</v>
-          </cell>
-          <cell r="N394" t="str">
-            <v>2012 - 2013</v>
-          </cell>
-          <cell r="O394" t="str">
-            <v>2013 - 2014</v>
-          </cell>
-          <cell r="P394" t="str">
-            <v>2014 - 2015</v>
-          </cell>
-          <cell r="Q394" t="str">
-            <v>2015 - 2016</v>
-          </cell>
-          <cell r="R394" t="str">
-            <v>2016 - 2017</v>
-          </cell>
-          <cell r="S394" t="str">
-            <v>2017 - 2018</v>
-          </cell>
-          <cell r="T394" t="str">
-            <v>2018 - 2019</v>
-          </cell>
-          <cell r="U394" t="str">
-            <v>2019 - 2020</v>
-          </cell>
-          <cell r="V394" t="str">
-            <v>2020 - 2021</v>
-          </cell>
-          <cell r="W394" t="str">
-            <v>2021 - 2022</v>
-          </cell>
-          <cell r="X394" t="str">
-            <v>2022 - 2023</v>
-          </cell>
-          <cell r="Y394" t="str">
-            <v>2023 - 2024</v>
-          </cell>
-          <cell r="Z394" t="str">
-            <v>2024 - 2025</v>
-          </cell>
-        </row>
-        <row r="396">
-          <cell r="B396">
-            <v>3.8562683489500387</v>
-          </cell>
-          <cell r="C396">
-            <v>9.2878291850552159</v>
-          </cell>
-          <cell r="D396">
-            <v>6.0428051145636488</v>
-          </cell>
-          <cell r="E396">
-            <v>19.998767119576328</v>
-          </cell>
-          <cell r="F396">
-            <v>7.4350511467602161</v>
-          </cell>
-          <cell r="G396">
-            <v>9.419780488144184</v>
-          </cell>
-          <cell r="H396">
-            <v>11.907004288213045</v>
-          </cell>
-          <cell r="I396">
-            <v>19.311584458678269</v>
-          </cell>
-          <cell r="J396">
-            <v>4.3995566697454791</v>
-          </cell>
-          <cell r="K396">
-            <v>5.9289755273239848</v>
-          </cell>
-          <cell r="L396">
-            <v>10.651156564646968</v>
-          </cell>
-          <cell r="M396">
-            <v>1.2943519713714409</v>
-          </cell>
-          <cell r="N396">
-            <v>3.7728134644513744</v>
-          </cell>
-          <cell r="O396">
-            <v>7.8222781287357037</v>
-          </cell>
-          <cell r="P396">
-            <v>-5.3884595491042973</v>
-          </cell>
-          <cell r="Q396">
-            <v>0.71146397623145674</v>
-          </cell>
-          <cell r="R396">
-            <v>9.1743592984062019</v>
-          </cell>
-          <cell r="S396">
-            <v>4.5469930768544202</v>
-          </cell>
-          <cell r="T396">
-            <v>-2.3304999357333713</v>
-          </cell>
-          <cell r="U396">
-            <v>6.2086830642616775</v>
-          </cell>
-          <cell r="V396">
-            <v>6.8946280591658962</v>
-          </cell>
-          <cell r="W396">
-            <v>7.6543502080105981</v>
-          </cell>
-          <cell r="X396">
-            <v>8.6248310999405646</v>
-          </cell>
-          <cell r="Y396">
-            <v>5.0943457973083923</v>
-          </cell>
-          <cell r="Z396">
-            <v>0.22392066090787921</v>
-          </cell>
-        </row>
-        <row r="397">
-          <cell r="B397">
-            <v>8.5977263466860308</v>
-          </cell>
-          <cell r="C397">
-            <v>7.7508822699549569</v>
-          </cell>
-          <cell r="D397">
-            <v>7.6842439060482661</v>
-          </cell>
-          <cell r="E397">
-            <v>9.8351437395220529</v>
-          </cell>
-          <cell r="F397">
-            <v>11.790161369020112</v>
-          </cell>
-          <cell r="G397">
-            <v>9.5503494617030782</v>
-          </cell>
-          <cell r="H397">
-            <v>8.3735850397367528</v>
-          </cell>
-          <cell r="I397">
-            <v>11.037279142134111</v>
-          </cell>
-          <cell r="J397">
-            <v>0.27307167938968746</v>
-          </cell>
-          <cell r="K397">
-            <v>14.929498856953401</v>
-          </cell>
-          <cell r="L397">
-            <v>4.5879765064649831</v>
-          </cell>
-          <cell r="M397">
-            <v>9.2402278727153941</v>
-          </cell>
-          <cell r="N397">
-            <v>6.7853948276301708</v>
-          </cell>
-          <cell r="O397">
-            <v>10.563465472400679</v>
-          </cell>
-          <cell r="P397">
-            <v>3.6598674343968298</v>
-          </cell>
-          <cell r="Q397">
-            <v>7.8233876950490497</v>
-          </cell>
-          <cell r="R397">
-            <v>8.836331365596422</v>
-          </cell>
-          <cell r="S397">
-            <v>11.920281512291297</v>
-          </cell>
-          <cell r="T397">
-            <v>6.0323273883342381</v>
-          </cell>
-          <cell r="U397">
-            <v>-13.8707610612623</v>
-          </cell>
-          <cell r="V397">
-            <v>9.9928242723429861</v>
-          </cell>
-          <cell r="W397">
-            <v>14.787659207089547</v>
-          </cell>
-          <cell r="X397">
-            <v>6.5079304707486898</v>
-          </cell>
-          <cell r="Y397">
-            <v>6.8292801099833582</v>
-          </cell>
-          <cell r="Z397">
-            <v>3.0778534327532867</v>
-          </cell>
-        </row>
-        <row r="402">
-          <cell r="B402">
-            <v>10.364849667386665</v>
-          </cell>
-          <cell r="C402">
-            <v>8.0390035321422459</v>
-          </cell>
-          <cell r="D402">
-            <v>9.5732951684526597</v>
-          </cell>
-          <cell r="E402">
-            <v>13.037698351205805</v>
-          </cell>
-          <cell r="F402">
-            <v>11.722255830661936</v>
-          </cell>
-          <cell r="G402">
-            <v>11.766191697825647</v>
-          </cell>
-          <cell r="H402">
-            <v>10.337202724937484</v>
-          </cell>
-          <cell r="I402">
-            <v>10.423862098628149</v>
-          </cell>
-          <cell r="J402">
-            <v>6.6354614066437705</v>
-          </cell>
-          <cell r="K402">
-            <v>11.972661224691805</v>
-          </cell>
-          <cell r="L402">
-            <v>9.2375162802133417</v>
-          </cell>
-          <cell r="M402">
-            <v>10.905136199575566</v>
-          </cell>
-          <cell r="N402">
-            <v>11.397354569169522</v>
-          </cell>
-          <cell r="O402">
-            <v>9.4591787574127721</v>
-          </cell>
-          <cell r="P402">
-            <v>9.011679201597957</v>
-          </cell>
-          <cell r="Q402">
-            <v>10.352334328074122</v>
-          </cell>
-          <cell r="R402">
-            <v>9.7458376019097699</v>
-          </cell>
-          <cell r="S402">
-            <v>10.496084067641689</v>
-          </cell>
-          <cell r="T402">
-            <v>8.7636468856581757</v>
-          </cell>
-          <cell r="U402">
-            <v>-7.1745559504802117</v>
-          </cell>
-          <cell r="V402">
-            <v>7.4696296571646172</v>
-          </cell>
-          <cell r="W402">
-            <v>13.831464849151388</v>
-          </cell>
-          <cell r="X402">
-            <v>12.492548522477051</v>
-          </cell>
-          <cell r="Y402">
-            <v>10.20400234643526</v>
-          </cell>
-          <cell r="Z402">
-            <v>7.9968138097116679</v>
-          </cell>
-        </row>
-        <row r="415">
-          <cell r="B415">
-            <v>8.8394257352917975</v>
-          </cell>
-          <cell r="C415">
-            <v>8.1045849777290329</v>
-          </cell>
-          <cell r="D415">
-            <v>8.4414233474862925</v>
-          </cell>
-          <cell r="E415">
-            <v>12.846964435412318</v>
-          </cell>
-          <cell r="F415">
-            <v>11.145544777261463</v>
-          </cell>
-          <cell r="G415">
-            <v>10.699756738487977</v>
-          </cell>
-          <cell r="H415">
-            <v>9.8898705788279955</v>
-          </cell>
-          <cell r="I415">
-            <v>11.835603624048161</v>
-          </cell>
-          <cell r="J415">
-            <v>4.2262404595586389</v>
-          </cell>
-          <cell r="K415">
-            <v>12.025966836852348</v>
-          </cell>
-          <cell r="L415">
-            <v>7.9282352542534511</v>
-          </cell>
-          <cell r="M415">
-            <v>9.0286651696070948</v>
-          </cell>
-          <cell r="N415">
-            <v>8.9507273876512414</v>
-          </cell>
-          <cell r="O415">
-            <v>9.5948503520951931</v>
-          </cell>
-          <cell r="P415">
-            <v>5.5829392343181468</v>
-          </cell>
-          <cell r="Q415">
-            <v>8.5213038282147835</v>
-          </cell>
-          <cell r="R415">
-            <v>9.4120652182858748</v>
-          </cell>
-          <cell r="S415">
-            <v>10.319352424276644</v>
-          </cell>
-          <cell r="T415">
-            <v>6.8582527519006788</v>
-          </cell>
-          <cell r="U415">
-            <v>-8.0249030741325669</v>
-          </cell>
-          <cell r="V415">
-            <v>8.1276491471909793</v>
-          </cell>
-          <cell r="W415">
-            <v>13.485723769004537</v>
-          </cell>
-          <cell r="X415">
-            <v>10.374333525482555</v>
-          </cell>
-          <cell r="Y415">
-            <v>8.772084465490579</v>
-          </cell>
-          <cell r="Z415">
-            <v>5.9285829032294401</v>
-          </cell>
-        </row>
-        <row r="435">
-          <cell r="B435">
-            <v>3.8639288662351419</v>
-          </cell>
-          <cell r="C435">
-            <v>3.6080425204229698</v>
-          </cell>
-          <cell r="D435">
-            <v>4.5747486592166098</v>
-          </cell>
-          <cell r="E435">
-            <v>4.9891114832411034</v>
-          </cell>
-          <cell r="F435">
-            <v>3.4969126446215455</v>
-          </cell>
-          <cell r="G435">
-            <v>4.5815351990400757</v>
-          </cell>
-          <cell r="H435">
-            <v>5.3700163362550484</v>
-          </cell>
-          <cell r="I435">
-            <v>3.3900642948923689</v>
-          </cell>
-          <cell r="J435">
-            <v>-0.14469733608144963</v>
-          </cell>
-          <cell r="K435">
-            <v>1.3237302684346588</v>
-          </cell>
-          <cell r="L435">
-            <v>3.3840782714027</v>
-          </cell>
-          <cell r="M435">
-            <v>3.0799487738872813</v>
-          </cell>
-          <cell r="N435">
-            <v>2.9331064222362357</v>
-          </cell>
-          <cell r="O435">
-            <v>1.8730139656827163</v>
-          </cell>
-          <cell r="P435">
-            <v>0.73611896593881454</v>
-          </cell>
-          <cell r="Q435">
-            <v>-0.96300132987261122</v>
-          </cell>
-          <cell r="R435">
-            <v>4.2491447423698645</v>
-          </cell>
-          <cell r="S435">
-            <v>1.1176535637619054</v>
-          </cell>
-          <cell r="T435">
-            <v>1.204950181773043</v>
-          </cell>
-          <cell r="U435">
-            <v>-0.19421886196009552</v>
-          </cell>
-          <cell r="V435">
-            <v>-0.2909612687144687</v>
-          </cell>
-          <cell r="W435">
-            <v>0.48018751594077003</v>
-          </cell>
-          <cell r="X435">
-            <v>1.2043335890745936</v>
-          </cell>
-          <cell r="Y435">
-            <v>-1.4946813342777432</v>
-          </cell>
-          <cell r="Z435">
-            <v>3.0859917831299555</v>
-          </cell>
-        </row>
-        <row r="436">
-          <cell r="B436">
-            <v>1.3379502482438141</v>
-          </cell>
-          <cell r="C436">
-            <v>3.6748651649366906</v>
-          </cell>
-          <cell r="D436">
-            <v>4.9645694771510023</v>
-          </cell>
-          <cell r="E436">
-            <v>4.4068792758271229</v>
-          </cell>
-          <cell r="F436">
-            <v>5.0508709302653472</v>
-          </cell>
-          <cell r="G436">
-            <v>3.7320716864625894</v>
-          </cell>
-          <cell r="H436">
-            <v>4.945437868198681</v>
-          </cell>
-          <cell r="I436">
-            <v>5.4714985552338078</v>
-          </cell>
-          <cell r="J436">
-            <v>-1.416099240391361</v>
-          </cell>
-          <cell r="K436">
-            <v>9.8235825205154299</v>
-          </cell>
-          <cell r="L436">
-            <v>1.6017135235883728</v>
-          </cell>
-          <cell r="M436">
-            <v>7.68801960078018</v>
-          </cell>
-          <cell r="N436">
-            <v>6.8155009548634666</v>
-          </cell>
-          <cell r="O436">
-            <v>7.5003612810670575</v>
-          </cell>
-          <cell r="P436">
-            <v>6.5069084534475934</v>
-          </cell>
-          <cell r="Q436">
-            <v>8.1887349340195641</v>
-          </cell>
-          <cell r="R436">
-            <v>7.019457759628466</v>
-          </cell>
-          <cell r="S436">
-            <v>7.302984107180805</v>
-          </cell>
-          <cell r="T436">
-            <v>5.4696287387019993</v>
-          </cell>
-          <cell r="U436">
-            <v>-13.121097355718078</v>
-          </cell>
-          <cell r="V436">
-            <v>8.5294081090508342</v>
-          </cell>
-          <cell r="W436">
-            <v>6.5228829965925428</v>
-          </cell>
-          <cell r="X436">
-            <v>3.6269357928687924</v>
-          </cell>
-          <cell r="Y436">
-            <v>5.6399069224808471</v>
-          </cell>
-          <cell r="Z436">
-            <v>1.5239268382415645</v>
-          </cell>
-        </row>
-        <row r="441">
-          <cell r="B441">
-            <v>3.8504730238576883</v>
-          </cell>
-          <cell r="C441">
-            <v>3.771936081718394</v>
-          </cell>
-          <cell r="D441">
-            <v>5.3066814298613991</v>
-          </cell>
-          <cell r="E441">
-            <v>8.2936780316530161</v>
-          </cell>
-          <cell r="F441">
-            <v>5.2819632342929594</v>
-          </cell>
-          <cell r="G441">
-            <v>6.4136363188305126</v>
-          </cell>
-          <cell r="H441">
-            <v>7.695710341755003</v>
-          </cell>
-          <cell r="I441">
-            <v>3.9886933128141351</v>
-          </cell>
-          <cell r="J441">
-            <v>3.4257677575938175</v>
-          </cell>
-          <cell r="K441">
-            <v>7.553215154649223</v>
-          </cell>
-          <cell r="L441">
-            <v>5.1684657298538923</v>
-          </cell>
-          <cell r="M441">
-            <v>7.3808691902351313</v>
-          </cell>
-          <cell r="N441">
-            <v>7.5711768242778987</v>
-          </cell>
-          <cell r="O441">
-            <v>6.7174996920232246</v>
-          </cell>
-          <cell r="P441">
-            <v>7.4136407800169764</v>
-          </cell>
-          <cell r="Q441">
-            <v>8.1741539634557085</v>
-          </cell>
-          <cell r="R441">
-            <v>7.3564353009879113</v>
-          </cell>
-          <cell r="S441">
-            <v>6.742605900669929</v>
-          </cell>
-          <cell r="T441">
-            <v>7.2433588277661158</v>
-          </cell>
-          <cell r="U441">
-            <v>-9.1272079402560991</v>
-          </cell>
-          <cell r="V441">
-            <v>5.3665446534042758</v>
-          </cell>
-          <cell r="W441">
-            <v>9.2289937899219012</v>
-          </cell>
-          <cell r="X441">
-            <v>7.0608205359761627</v>
-          </cell>
-          <cell r="Y441">
-            <v>6.7057387530641535</v>
-          </cell>
-          <cell r="Z441">
-            <v>5.9030673752943841</v>
-          </cell>
-        </row>
-        <row r="454">
-          <cell r="B454">
-            <v>3.0492313441098133</v>
-          </cell>
-          <cell r="C454">
-            <v>3.7162550018348526</v>
-          </cell>
-          <cell r="D454">
-            <v>5.0869111341206121</v>
-          </cell>
-          <cell r="E454">
-            <v>6.569228512800791</v>
-          </cell>
-          <cell r="F454">
-            <v>4.9425051178358075</v>
-          </cell>
-          <cell r="G454">
-            <v>5.3164168221744461</v>
-          </cell>
-          <cell r="H454">
-            <v>6.5192915503707241</v>
-          </cell>
-          <cell r="I454">
-            <v>4.344487304883387</v>
-          </cell>
-          <cell r="J454">
-            <v>1.4483230628297576</v>
-          </cell>
-          <cell r="K454">
-            <v>7.3344999604172898</v>
-          </cell>
-          <cell r="L454">
-            <v>3.8582328274785311</v>
-          </cell>
-          <cell r="M454">
-            <v>6.8969517105742</v>
-          </cell>
-          <cell r="N454">
-            <v>6.7505313017787785</v>
-          </cell>
-          <cell r="O454">
-            <v>6.3479874825022762</v>
-          </cell>
-          <cell r="P454">
-            <v>6.3483097167204932</v>
-          </cell>
-          <cell r="Q454">
-            <v>7.14945674959813</v>
-          </cell>
-          <cell r="R454">
-            <v>6.9309883258640355</v>
-          </cell>
-          <cell r="S454">
-            <v>6.3414855714878371</v>
-          </cell>
-          <cell r="T454">
-            <v>6.118525662562547</v>
-          </cell>
-          <cell r="U454">
-            <v>-9.518294740699119</v>
-          </cell>
-          <cell r="V454">
-            <v>5.7147331321929471</v>
-          </cell>
-          <cell r="W454">
-            <v>7.5809821277173199</v>
-          </cell>
-          <cell r="X454">
-            <v>5.5189496785154546</v>
-          </cell>
-          <cell r="Y454">
-            <v>5.6920161281656618</v>
-          </cell>
-          <cell r="Z454">
-            <v>4.403389306011249</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14624,9 +12652,8 @@
       </c>
     </row>
     <row r="3" spans="1:81" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="str">
-        <f>[1]Annual!A3</f>
-        <v>As of January 2026</v>
+      <c r="A3" s="14" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:81" x14ac:dyDescent="0.2">
@@ -15063,108 +13090,82 @@
         <v>508644.29562133801</v>
       </c>
       <c r="BD10" s="19">
-        <f>[1]Annual!B88</f>
         <v>515479.83105914737</v>
       </c>
       <c r="BE10" s="19">
-        <f>[1]Annual!C88</f>
         <v>535358.11662950239</v>
       </c>
       <c r="BF10" s="19">
-        <f>[1]Annual!D88</f>
         <v>585081.26403037924</v>
       </c>
       <c r="BG10" s="19">
-        <f>[1]Annual!E88</f>
         <v>620436.58457756066</v>
       </c>
       <c r="BH10" s="19">
-        <f>[1]Annual!F88</f>
         <v>744516.25225188024</v>
       </c>
       <c r="BI10" s="19">
-        <f>[1]Annual!G88</f>
         <v>799871.41640274995</v>
       </c>
       <c r="BJ10" s="19">
-        <f>[1]Annual!H88</f>
         <v>875217.54801529867</v>
       </c>
       <c r="BK10" s="19">
-        <f>[1]Annual!I88</f>
         <v>979429.73898867343</v>
       </c>
       <c r="BL10" s="19">
-        <f>[1]Annual!J88</f>
         <v>1168573.1402468833</v>
       </c>
       <c r="BM10" s="19">
-        <f>[1]Annual!K88</f>
         <v>1219985.1777794692</v>
       </c>
       <c r="BN10" s="19">
-        <f>[1]Annual!L88</f>
         <v>1292317.8004069938</v>
       </c>
       <c r="BO10" s="19">
-        <f>[1]Annual!M88</f>
         <v>1429964.5926411448</v>
       </c>
       <c r="BP10" s="19">
-        <f>[1]Annual!N88</f>
         <v>1448473.3675359092</v>
       </c>
       <c r="BQ10" s="19">
-        <f>[1]Annual!O88</f>
         <v>1503121.5657752962</v>
       </c>
       <c r="BR10" s="19">
-        <f>[1]Annual!P88</f>
         <v>1620699.915263247</v>
       </c>
       <c r="BS10" s="19">
-        <f>[1]Annual!Q88</f>
         <v>1533369.1559169192</v>
       </c>
       <c r="BT10" s="19">
-        <f>[1]Annual!R88</f>
         <v>1544278.5250839123</v>
       </c>
       <c r="BU10" s="19">
-        <f>[1]Annual!S88</f>
         <v>1685956.1855432384</v>
       </c>
       <c r="BV10" s="19">
-        <f>[1]Annual!T88</f>
         <v>1762616.4965786883</v>
       </c>
       <c r="BW10" s="19">
-        <f>[1]Annual!U88</f>
         <v>1721538.720258696</v>
       </c>
       <c r="BX10" s="19">
-        <f>[1]Annual!V88</f>
         <v>1828423.603228105</v>
       </c>
       <c r="BY10" s="19">
-        <f>[1]Annual!W88</f>
         <v>1954486.610016682</v>
       </c>
       <c r="BZ10" s="19">
-        <f>[1]Annual!X88</f>
         <v>2104089.8599160332</v>
       </c>
       <c r="CA10" s="19">
-        <f>[1]Annual!Y88</f>
         <v>2285564.0565247671</v>
       </c>
       <c r="CB10" s="19">
-        <f>[1]Annual!Z88</f>
-        <v>2401998.5929831276</v>
+        <v>2403539.1151501127</v>
       </c>
       <c r="CC10" s="19">
-        <f>[1]Annual!AA88</f>
-        <v>2407377.1641075336</v>
+        <v>2406532.3248881213</v>
       </c>
     </row>
     <row r="11" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -15334,108 +13335,82 @@
         <v>1123139.21148392</v>
       </c>
       <c r="BD11" s="19">
-        <f>[1]Annual!B89</f>
         <v>1293230.8123216361</v>
       </c>
       <c r="BE11" s="19">
-        <f>[1]Annual!C89</f>
         <v>1404419.2585960752</v>
       </c>
       <c r="BF11" s="19">
-        <f>[1]Annual!D89</f>
         <v>1513274.1419064312</v>
       </c>
       <c r="BG11" s="19">
-        <f>[1]Annual!E89</f>
         <v>1629557.8179376805</v>
       </c>
       <c r="BH11" s="19">
-        <f>[1]Annual!F89</f>
         <v>1789827.1716504705</v>
       </c>
       <c r="BI11" s="19">
-        <f>[1]Annual!G89</f>
         <v>2000850.6834146297</v>
       </c>
       <c r="BJ11" s="19">
-        <f>[1]Annual!H89</f>
         <v>2191938.9158876012</v>
       </c>
       <c r="BK11" s="19">
-        <f>[1]Annual!I89</f>
         <v>2375482.7850285335</v>
       </c>
       <c r="BL11" s="19">
-        <f>[1]Annual!J89</f>
         <v>2637671.450985474</v>
       </c>
       <c r="BM11" s="19">
-        <f>[1]Annual!K89</f>
         <v>2644874.1847134624</v>
       </c>
       <c r="BN11" s="19">
-        <f>[1]Annual!L89</f>
         <v>3039740.6458881143</v>
       </c>
       <c r="BO11" s="19">
-        <f>[1]Annual!M89</f>
         <v>3179203.2325789281</v>
       </c>
       <c r="BP11" s="19">
-        <f>[1]Annual!N89</f>
         <v>3472968.8558059549</v>
       </c>
       <c r="BQ11" s="19">
-        <f>[1]Annual!O89</f>
         <v>3708623.5049130186</v>
       </c>
       <c r="BR11" s="19">
-        <f>[1]Annual!P89</f>
         <v>4100382.6683558412</v>
       </c>
       <c r="BS11" s="19">
-        <f>[1]Annual!Q89</f>
         <v>4250451.2383206487</v>
       </c>
       <c r="BT11" s="19">
-        <f>[1]Annual!R89</f>
         <v>4582980.5174834859</v>
       </c>
       <c r="BU11" s="19">
-        <f>[1]Annual!S89</f>
         <v>4987947.8624290526</v>
       </c>
       <c r="BV11" s="19">
-        <f>[1]Annual!T89</f>
         <v>5582525.2893169122</v>
       </c>
       <c r="BW11" s="19">
-        <f>[1]Annual!U89</f>
         <v>5919281.4913050616</v>
       </c>
       <c r="BX11" s="19">
-        <f>[1]Annual!V89</f>
         <v>5098232.0991026126</v>
       </c>
       <c r="BY11" s="19">
-        <f>[1]Annual!W89</f>
         <v>5607689.4737621192</v>
       </c>
       <c r="BZ11" s="19">
-        <f>[1]Annual!X89</f>
         <v>6436935.4825338945</v>
       </c>
       <c r="CA11" s="19">
-        <f>[1]Annual!Y89</f>
         <v>6855846.7681841524</v>
       </c>
       <c r="CB11" s="19">
-        <f>[1]Annual!Z89</f>
-        <v>7324051.7478946894</v>
+        <v>7322506.791982213</v>
       </c>
       <c r="CC11" s="19">
-        <f>[1]Annual!AA89</f>
-        <v>7549475.326033894</v>
+        <v>7559815.6804408217</v>
       </c>
     </row>
     <row r="12" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -15605,108 +13580,82 @@
         <v>1715803.6829949301</v>
       </c>
       <c r="BD12" s="19">
-        <f>[1]Annual!B94</f>
         <v>1888845.5620071718</v>
       </c>
       <c r="BE12" s="19">
-        <f>[1]Annual!C94</f>
         <v>2084621.56495832</v>
       </c>
       <c r="BF12" s="19">
-        <f>[1]Annual!D94</f>
         <v>2252204.3661971181</v>
       </c>
       <c r="BG12" s="19">
-        <f>[1]Annual!E94</f>
         <v>2467814.5379699469</v>
       </c>
       <c r="BH12" s="19">
-        <f>[1]Annual!F94</f>
         <v>2789560.7532976717</v>
       </c>
       <c r="BI12" s="19">
-        <f>[1]Annual!G94</f>
         <v>3116560.2013509646</v>
       </c>
       <c r="BJ12" s="19">
-        <f>[1]Annual!H94</f>
         <v>3483260.64902006</v>
       </c>
       <c r="BK12" s="19">
-        <f>[1]Annual!I94</f>
         <v>3843332.3637472363</v>
       </c>
       <c r="BL12" s="19">
-        <f>[1]Annual!J94</f>
         <v>4243956.0293361945</v>
       </c>
       <c r="BM12" s="19">
-        <f>[1]Annual!K94</f>
         <v>4525562.0937777292</v>
       </c>
       <c r="BN12" s="19">
-        <f>[1]Annual!L94</f>
         <v>5067392.3117788061</v>
       </c>
       <c r="BO12" s="19">
-        <f>[1]Annual!M94</f>
         <v>5535493.5015616529</v>
       </c>
       <c r="BP12" s="19">
-        <f>[1]Annual!N94</f>
         <v>6139146.6072256053</v>
       </c>
       <c r="BQ12" s="19">
-        <f>[1]Annual!O94</f>
         <v>6838846.913572249</v>
       </c>
       <c r="BR12" s="19">
-        <f>[1]Annual!P94</f>
         <v>7485745.6680728551</v>
       </c>
       <c r="BS12" s="19">
-        <f>[1]Annual!Q94</f>
         <v>8160337.0535270972</v>
       </c>
       <c r="BT12" s="19">
-        <f>[1]Annual!R94</f>
         <v>9005122.4276059344</v>
       </c>
       <c r="BU12" s="19">
-        <f>[1]Annual!S94</f>
         <v>9882747.0352535639</v>
       </c>
       <c r="BV12" s="19">
-        <f>[1]Annual!T94</f>
         <v>10920048.472266145</v>
       </c>
       <c r="BW12" s="19">
-        <f>[1]Annual!U94</f>
         <v>11877042.96011826</v>
       </c>
       <c r="BX12" s="19">
-        <f>[1]Annual!V94</f>
         <v>11024917.867682004</v>
       </c>
       <c r="BY12" s="19">
-        <f>[1]Annual!W94</f>
         <v>11848438.402404422</v>
       </c>
       <c r="BZ12" s="19">
-        <f>[1]Annual!X94</f>
         <v>13487250.995206343</v>
       </c>
       <c r="CA12" s="19">
-        <f>[1]Annual!Y94</f>
         <v>15172152.370130764</v>
       </c>
       <c r="CB12" s="19">
-        <f>[1]Annual!Z94</f>
-        <v>16720319.15398364</v>
+        <v>16723397.123838713</v>
       </c>
       <c r="CC12" s="19">
-        <f>[1]Annual!AA94</f>
-        <v>18057411.945117269</v>
+        <v>18043586.786567662</v>
       </c>
     </row>
     <row r="13" spans="1:81" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -15959,108 +13908,82 @@
         <v>3347587.1901001884</v>
       </c>
       <c r="BD14" s="24">
-        <f>[1]Annual!B107</f>
         <v>3697556.2053879555</v>
       </c>
       <c r="BE14" s="24">
-        <f>[1]Annual!C107</f>
         <v>4024398.9401838975</v>
       </c>
       <c r="BF14" s="24">
-        <f>[1]Annual!D107</f>
         <v>4350559.7721339278</v>
       </c>
       <c r="BG14" s="24">
-        <f>[1]Annual!E107</f>
         <v>4717808.9404851878</v>
       </c>
       <c r="BH14" s="24">
-        <f>[1]Annual!F107</f>
         <v>5323904.1772000222</v>
       </c>
       <c r="BI14" s="24">
-        <f>[1]Annual!G107</f>
         <v>5917282.301168344</v>
       </c>
       <c r="BJ14" s="24">
-        <f>[1]Annual!H107</f>
         <v>6550417.11292296</v>
       </c>
       <c r="BK14" s="24">
-        <f>[1]Annual!I107</f>
         <v>7198244.8877644427</v>
       </c>
       <c r="BL14" s="24">
-        <f>[1]Annual!J107</f>
         <v>8050200.6205685521</v>
       </c>
       <c r="BM14" s="24">
-        <f>[1]Annual!K107</f>
         <v>8390421.4562706612</v>
       </c>
       <c r="BN14" s="24">
-        <f>[1]Annual!L107</f>
         <v>9399450.7580739148</v>
       </c>
       <c r="BO14" s="24">
-        <f>[1]Annual!M107</f>
         <v>10144661.326781726</v>
       </c>
       <c r="BP14" s="24">
-        <f>[1]Annual!N107</f>
         <v>11060588.830567468</v>
       </c>
       <c r="BQ14" s="24">
-        <f>[1]Annual!O107</f>
         <v>12050591.984260563</v>
       </c>
       <c r="BR14" s="24">
-        <f>[1]Annual!P107</f>
         <v>13206828.251691943</v>
       </c>
       <c r="BS14" s="24">
-        <f>[1]Annual!Q107</f>
         <v>13944157.447764665</v>
       </c>
       <c r="BT14" s="24">
-        <f>[1]Annual!R107</f>
         <v>15132381.470173333</v>
       </c>
       <c r="BU14" s="24">
-        <f>[1]Annual!S107</f>
         <v>16556651.083225854</v>
       </c>
       <c r="BV14" s="24">
-        <f>[1]Annual!T107</f>
         <v>18265190.258161746</v>
       </c>
       <c r="BW14" s="24">
-        <f>[1]Annual!U107</f>
         <v>19517863.171682019</v>
       </c>
       <c r="BX14" s="24">
-        <f>[1]Annual!V107</f>
         <v>17951573.570012722</v>
       </c>
       <c r="BY14" s="24">
-        <f>[1]Annual!W107</f>
         <v>19410614.486183222</v>
       </c>
       <c r="BZ14" s="24">
-        <f>[1]Annual!X107</f>
         <v>22028276.337656271</v>
       </c>
       <c r="CA14" s="24">
-        <f>[1]Annual!Y107</f>
         <v>24313563.194839686</v>
       </c>
       <c r="CB14" s="24">
-        <f>[1]Annual!Z107</f>
-        <v>26446369.494861454</v>
+        <v>26449443.030971039</v>
       </c>
       <c r="CC14" s="24">
-        <f>[1]Annual!AA107</f>
-        <v>28014264.435258694</v>
+        <v>28009934.791896604</v>
       </c>
     </row>
     <row r="15" spans="1:81" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -16550,9 +14473,8 @@
       <c r="CC20" s="19"/>
     </row>
     <row r="21" spans="1:81" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="str">
-        <f>$A$3</f>
-        <v>As of January 2026</v>
+      <c r="A21" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
@@ -17220,105 +15142,80 @@
       <c r="BC27" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="BD27" s="28" t="str">
-        <f>[1]Annual!B394</f>
-        <v>2000 - 2001</v>
-      </c>
-      <c r="BE27" s="28" t="str">
-        <f>[1]Annual!C394</f>
-        <v>2001 - 2002</v>
-      </c>
-      <c r="BF27" s="28" t="str">
-        <f>[1]Annual!D394</f>
-        <v>2002 - 2003</v>
-      </c>
-      <c r="BG27" s="28" t="str">
-        <f>[1]Annual!E394</f>
-        <v>2003 - 2004</v>
-      </c>
-      <c r="BH27" s="28" t="str">
-        <f>[1]Annual!F394</f>
-        <v>2004 - 2005</v>
-      </c>
-      <c r="BI27" s="28" t="str">
-        <f>[1]Annual!G394</f>
-        <v>2005 - 2006</v>
-      </c>
-      <c r="BJ27" s="28" t="str">
-        <f>[1]Annual!H394</f>
-        <v>2006 - 2007</v>
-      </c>
-      <c r="BK27" s="28" t="str">
-        <f>[1]Annual!I394</f>
-        <v>2007 - 2008</v>
-      </c>
-      <c r="BL27" s="28" t="str">
-        <f>[1]Annual!J394</f>
-        <v>2008 - 2009</v>
-      </c>
-      <c r="BM27" s="28" t="str">
-        <f>[1]Annual!K394</f>
-        <v>2009 - 2010</v>
-      </c>
-      <c r="BN27" s="28" t="str">
-        <f>[1]Annual!L394</f>
-        <v>2010 - 2011</v>
-      </c>
-      <c r="BO27" s="28" t="str">
-        <f>[1]Annual!M394</f>
-        <v>2011 - 2012</v>
-      </c>
-      <c r="BP27" s="28" t="str">
-        <f>[1]Annual!N394</f>
-        <v>2012 - 2013</v>
-      </c>
-      <c r="BQ27" s="28" t="str">
-        <f>[1]Annual!O394</f>
-        <v>2013 - 2014</v>
-      </c>
-      <c r="BR27" s="28" t="str">
-        <f>[1]Annual!P394</f>
-        <v>2014 - 2015</v>
-      </c>
-      <c r="BS27" s="28" t="str">
-        <f>[1]Annual!Q394</f>
-        <v>2015 - 2016</v>
-      </c>
-      <c r="BT27" s="28" t="str">
-        <f>[1]Annual!R394</f>
-        <v>2016 - 2017</v>
-      </c>
-      <c r="BU27" s="28" t="str">
-        <f>[1]Annual!S394</f>
-        <v>2017 - 2018</v>
-      </c>
-      <c r="BV27" s="28" t="str">
-        <f>[1]Annual!T394</f>
-        <v>2018 - 2019</v>
-      </c>
-      <c r="BW27" s="28" t="str">
-        <f>[1]Annual!U394</f>
-        <v>2019 - 2020</v>
-      </c>
-      <c r="BX27" s="28" t="str">
-        <f>[1]Annual!V394</f>
-        <v>2020 - 2021</v>
-      </c>
-      <c r="BY27" s="28" t="str">
-        <f>[1]Annual!W394</f>
-        <v>2021 - 2022</v>
-      </c>
-      <c r="BZ27" s="28" t="str">
-        <f>[1]Annual!X394</f>
-        <v>2022 - 2023</v>
-      </c>
-      <c r="CA27" s="28" t="str">
-        <f>[1]Annual!Y394</f>
-        <v>2023 - 2024</v>
-      </c>
-      <c r="CB27" s="28" t="str">
-        <f>[1]Annual!Z394</f>
-        <v>2024 - 2025</v>
+      <c r="BD27" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="BE27" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="BF27" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG27" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH27" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="BI27" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="BJ27" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BK27" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="BL27" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="BM27" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="BN27" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="BO27" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="BP27" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="BQ27" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="BR27" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="BS27" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="BT27" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="BU27" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="BV27" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="BW27" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="BX27" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="BY27" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="BZ27" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="CA27" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="CB27" s="28" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -17488,104 +15385,79 @@
         <v>1.3438673032422486</v>
       </c>
       <c r="BD28" s="26">
-        <f>[1]Annual!B396</f>
         <v>3.8562683489500387</v>
       </c>
       <c r="BE28" s="26">
-        <f>[1]Annual!C396</f>
         <v>9.2878291850552159</v>
       </c>
       <c r="BF28" s="26">
-        <f>[1]Annual!D396</f>
         <v>6.0428051145636488</v>
       </c>
       <c r="BG28" s="26">
-        <f>[1]Annual!E396</f>
         <v>19.998767119576328</v>
       </c>
       <c r="BH28" s="26">
-        <f>[1]Annual!F396</f>
         <v>7.4350511467602161</v>
       </c>
       <c r="BI28" s="26">
-        <f>[1]Annual!G396</f>
         <v>9.419780488144184</v>
       </c>
       <c r="BJ28" s="26">
-        <f>[1]Annual!H396</f>
         <v>11.907004288213045</v>
       </c>
       <c r="BK28" s="26">
-        <f>[1]Annual!I396</f>
         <v>19.311584458678269</v>
       </c>
       <c r="BL28" s="26">
-        <f>[1]Annual!J396</f>
         <v>4.3995566697454791</v>
       </c>
       <c r="BM28" s="26">
-        <f>[1]Annual!K396</f>
         <v>5.9289755273239848</v>
       </c>
       <c r="BN28" s="26">
-        <f>[1]Annual!L396</f>
         <v>10.651156564646968</v>
       </c>
       <c r="BO28" s="26">
-        <f>[1]Annual!M396</f>
         <v>1.2943519713714409</v>
       </c>
       <c r="BP28" s="26">
-        <f>[1]Annual!N396</f>
         <v>3.7728134644513744</v>
       </c>
       <c r="BQ28" s="26">
-        <f>[1]Annual!O396</f>
         <v>7.8222781287357037</v>
       </c>
       <c r="BR28" s="26">
-        <f>[1]Annual!P396</f>
         <v>-5.3884595491042973</v>
       </c>
       <c r="BS28" s="26">
-        <f>[1]Annual!Q396</f>
         <v>0.71146397623145674</v>
       </c>
       <c r="BT28" s="26">
-        <f>[1]Annual!R396</f>
         <v>9.1743592984062019</v>
       </c>
       <c r="BU28" s="26">
-        <f>[1]Annual!S396</f>
         <v>4.5469930768544202</v>
       </c>
       <c r="BV28" s="26">
-        <f>[1]Annual!T396</f>
         <v>-2.3304999357333713</v>
       </c>
       <c r="BW28" s="34">
-        <f>[1]Annual!U396</f>
         <v>6.2086830642616775</v>
       </c>
       <c r="BX28" s="34">
-        <f>[1]Annual!V396</f>
         <v>6.8946280591658962</v>
       </c>
       <c r="BY28" s="34">
-        <f>[1]Annual!W396</f>
         <v>7.6543502080105981</v>
       </c>
       <c r="BZ28" s="34">
-        <f>[1]Annual!X396</f>
         <v>8.6248310999405646</v>
       </c>
       <c r="CA28" s="34">
-        <f>[1]Annual!Y396</f>
-        <v>5.0943457973083923</v>
+        <v>5.1617480721467359</v>
       </c>
       <c r="CB28" s="34">
-        <f>[1]Annual!Z396</f>
-        <v>0.22392066090787921</v>
+        <v>0.12453343151945262</v>
       </c>
     </row>
     <row r="29" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -17755,104 +15627,79 @@
         <v>15.144301505719014</v>
       </c>
       <c r="BD29" s="26">
-        <f>[1]Annual!B397</f>
         <v>8.5977263466860308</v>
       </c>
       <c r="BE29" s="26">
-        <f>[1]Annual!C397</f>
         <v>7.7508822699549569</v>
       </c>
       <c r="BF29" s="26">
-        <f>[1]Annual!D397</f>
         <v>7.6842439060482661</v>
       </c>
       <c r="BG29" s="26">
-        <f>[1]Annual!E397</f>
         <v>9.8351437395220529</v>
       </c>
       <c r="BH29" s="26">
-        <f>[1]Annual!F397</f>
         <v>11.790161369020112</v>
       </c>
       <c r="BI29" s="26">
-        <f>[1]Annual!G397</f>
         <v>9.5503494617030782</v>
       </c>
       <c r="BJ29" s="26">
-        <f>[1]Annual!H397</f>
         <v>8.3735850397367528</v>
       </c>
       <c r="BK29" s="26">
-        <f>[1]Annual!I397</f>
         <v>11.037279142134111</v>
       </c>
       <c r="BL29" s="26">
-        <f>[1]Annual!J397</f>
         <v>0.27307167938968746</v>
       </c>
       <c r="BM29" s="26">
-        <f>[1]Annual!K397</f>
         <v>14.929498856953401</v>
       </c>
       <c r="BN29" s="26">
-        <f>[1]Annual!L397</f>
         <v>4.5879765064649831</v>
       </c>
       <c r="BO29" s="26">
-        <f>[1]Annual!M397</f>
         <v>9.2402278727153941</v>
       </c>
       <c r="BP29" s="26">
-        <f>[1]Annual!N397</f>
         <v>6.7853948276301708</v>
       </c>
       <c r="BQ29" s="26">
-        <f>[1]Annual!O397</f>
         <v>10.563465472400679</v>
       </c>
       <c r="BR29" s="26">
-        <f>[1]Annual!P397</f>
         <v>3.6598674343968298</v>
       </c>
       <c r="BS29" s="26">
-        <f>[1]Annual!Q397</f>
         <v>7.8233876950490497</v>
       </c>
       <c r="BT29" s="26">
-        <f>[1]Annual!R397</f>
         <v>8.836331365596422</v>
       </c>
       <c r="BU29" s="26">
-        <f>[1]Annual!S397</f>
         <v>11.920281512291297</v>
       </c>
       <c r="BV29" s="26">
-        <f>[1]Annual!T397</f>
         <v>6.0323273883342381</v>
       </c>
       <c r="BW29" s="34">
-        <f>[1]Annual!U397</f>
         <v>-13.8707610612623</v>
       </c>
       <c r="BX29" s="34">
-        <f>[1]Annual!V397</f>
         <v>9.9928242723429861</v>
       </c>
       <c r="BY29" s="34">
-        <f>[1]Annual!W397</f>
         <v>14.787659207089547</v>
       </c>
       <c r="BZ29" s="34">
-        <f>[1]Annual!X397</f>
         <v>6.5079304707486898</v>
       </c>
       <c r="CA29" s="34">
-        <f>[1]Annual!Y397</f>
-        <v>6.8292801099833582</v>
+        <v>6.8067452435442988</v>
       </c>
       <c r="CB29" s="34">
-        <f>[1]Annual!Z397</f>
-        <v>3.0778534327532867</v>
+        <v>3.2408148629981497</v>
       </c>
     </row>
     <row r="30" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -18022,104 +15869,79 @@
         <v>10.085181581090083</v>
       </c>
       <c r="BD30" s="26">
-        <f>[1]Annual!B402</f>
         <v>10.364849667386665</v>
       </c>
       <c r="BE30" s="26">
-        <f>[1]Annual!C402</f>
         <v>8.0390035321422459</v>
       </c>
       <c r="BF30" s="26">
-        <f>[1]Annual!D402</f>
         <v>9.5732951684526597</v>
       </c>
       <c r="BG30" s="26">
-        <f>[1]Annual!E402</f>
         <v>13.037698351205805</v>
       </c>
       <c r="BH30" s="26">
-        <f>[1]Annual!F402</f>
         <v>11.722255830661936</v>
       </c>
       <c r="BI30" s="26">
-        <f>[1]Annual!G402</f>
         <v>11.766191697825647</v>
       </c>
       <c r="BJ30" s="26">
-        <f>[1]Annual!H402</f>
         <v>10.337202724937484</v>
       </c>
       <c r="BK30" s="26">
-        <f>[1]Annual!I402</f>
         <v>10.423862098628149</v>
       </c>
       <c r="BL30" s="26">
-        <f>[1]Annual!J402</f>
         <v>6.6354614066437705</v>
       </c>
       <c r="BM30" s="26">
-        <f>[1]Annual!K402</f>
         <v>11.972661224691805</v>
       </c>
       <c r="BN30" s="26">
-        <f>[1]Annual!L402</f>
         <v>9.2375162802133417</v>
       </c>
       <c r="BO30" s="26">
-        <f>[1]Annual!M402</f>
         <v>10.905136199575566</v>
       </c>
       <c r="BP30" s="26">
-        <f>[1]Annual!N402</f>
         <v>11.397354569169522</v>
       </c>
       <c r="BQ30" s="26">
-        <f>[1]Annual!O402</f>
         <v>9.4591787574127721</v>
       </c>
       <c r="BR30" s="26">
-        <f>[1]Annual!P402</f>
         <v>9.011679201597957</v>
       </c>
       <c r="BS30" s="26">
-        <f>[1]Annual!Q402</f>
         <v>10.352334328074122</v>
       </c>
       <c r="BT30" s="26">
-        <f>[1]Annual!R402</f>
         <v>9.7458376019097699</v>
       </c>
       <c r="BU30" s="26">
-        <f>[1]Annual!S402</f>
         <v>10.496084067641689</v>
       </c>
       <c r="BV30" s="26">
-        <f>[1]Annual!T402</f>
         <v>8.7636468856581757</v>
       </c>
       <c r="BW30" s="34">
-        <f>[1]Annual!U402</f>
         <v>-7.1745559504802117</v>
       </c>
       <c r="BX30" s="34">
-        <f>[1]Annual!V402</f>
         <v>7.4696296571646172</v>
       </c>
       <c r="BY30" s="34">
-        <f>[1]Annual!W402</f>
         <v>13.831464849151388</v>
       </c>
       <c r="BZ30" s="34">
-        <f>[1]Annual!X402</f>
         <v>12.492548522477051</v>
       </c>
       <c r="CA30" s="34">
-        <f>[1]Annual!Y402</f>
-        <v>10.20400234643526</v>
+        <v>10.224289315482139</v>
       </c>
       <c r="CB30" s="34">
-        <f>[1]Annual!Z402</f>
-        <v>7.9968138097116679</v>
+        <v>7.8942672529557854</v>
       </c>
     </row>
     <row r="31" spans="1:81" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -18371,104 +16193,79 @@
         <v>10.454365787238459</v>
       </c>
       <c r="BD32" s="27">
-        <f>[1]Annual!B415</f>
         <v>8.8394257352917975</v>
       </c>
       <c r="BE32" s="27">
-        <f>[1]Annual!C415</f>
         <v>8.1045849777290329</v>
       </c>
       <c r="BF32" s="27">
-        <f>[1]Annual!D415</f>
         <v>8.4414233474862925</v>
       </c>
       <c r="BG32" s="27">
-        <f>[1]Annual!E415</f>
         <v>12.846964435412318</v>
       </c>
       <c r="BH32" s="27">
-        <f>[1]Annual!F415</f>
         <v>11.145544777261463</v>
       </c>
       <c r="BI32" s="27">
-        <f>[1]Annual!G415</f>
         <v>10.699756738487977</v>
       </c>
       <c r="BJ32" s="27">
-        <f>[1]Annual!H415</f>
         <v>9.8898705788279955</v>
       </c>
       <c r="BK32" s="27">
-        <f>[1]Annual!I415</f>
         <v>11.835603624048161</v>
       </c>
       <c r="BL32" s="27">
-        <f>[1]Annual!J415</f>
         <v>4.2262404595586389</v>
       </c>
       <c r="BM32" s="27">
-        <f>[1]Annual!K415</f>
         <v>12.025966836852348</v>
       </c>
       <c r="BN32" s="27">
-        <f>[1]Annual!L415</f>
         <v>7.9282352542534511</v>
       </c>
       <c r="BO32" s="27">
-        <f>[1]Annual!M415</f>
         <v>9.0286651696070948</v>
       </c>
       <c r="BP32" s="27">
-        <f>[1]Annual!N415</f>
         <v>8.9507273876512414</v>
       </c>
       <c r="BQ32" s="27">
-        <f>[1]Annual!O415</f>
         <v>9.5948503520951931</v>
       </c>
       <c r="BR32" s="27">
-        <f>[1]Annual!P415</f>
         <v>5.5829392343181468</v>
       </c>
       <c r="BS32" s="27">
-        <f>[1]Annual!Q415</f>
         <v>8.5213038282147835</v>
       </c>
       <c r="BT32" s="27">
-        <f>[1]Annual!R415</f>
         <v>9.4120652182858748</v>
       </c>
       <c r="BU32" s="27">
-        <f>[1]Annual!S415</f>
         <v>10.319352424276644</v>
       </c>
       <c r="BV32" s="27">
-        <f>[1]Annual!T415</f>
         <v>6.8582527519006788</v>
       </c>
       <c r="BW32" s="27">
-        <f>[1]Annual!U415</f>
         <v>-8.0249030741325669</v>
       </c>
       <c r="BX32" s="27">
-        <f>[1]Annual!V415</f>
         <v>8.1276491471909793</v>
       </c>
       <c r="BY32" s="27">
-        <f>[1]Annual!W415</f>
         <v>13.485723769004537</v>
       </c>
       <c r="BZ32" s="27">
-        <f>[1]Annual!X415</f>
         <v>10.374333525482555</v>
       </c>
       <c r="CA32" s="27">
-        <f>[1]Annual!Y415</f>
-        <v>8.772084465490579</v>
+        <v>8.7847257064512547</v>
       </c>
       <c r="CB32" s="27">
-        <f>[1]Annual!Z415</f>
-        <v>5.9285829032294401</v>
+        <v>5.8999040512811547</v>
       </c>
     </row>
     <row r="33" spans="1:81" x14ac:dyDescent="0.2">
@@ -18891,9 +16688,8 @@
       <c r="CC38" s="19"/>
     </row>
     <row r="39" spans="1:81" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="str">
-        <f>$A$3</f>
-        <v>As of January 2026</v>
+      <c r="A39" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="19"/>
@@ -19809,108 +17605,82 @@
         <v>15.194355418898439</v>
       </c>
       <c r="BD46" s="22">
-        <f>[1]Annual!B242</f>
         <v>13.941095210615254</v>
       </c>
       <c r="BE46" s="22">
-        <f>[1]Annual!C242</f>
         <v>13.302809303618366</v>
       </c>
       <c r="BF46" s="22">
-        <f>[1]Annual!D242</f>
         <v>13.44841341516381</v>
       </c>
       <c r="BG46" s="22">
-        <f>[1]Annual!E242</f>
         <v>13.150947662449294</v>
       </c>
       <c r="BH46" s="22">
-        <f>[1]Annual!F242</f>
         <v>13.984403690816247</v>
       </c>
       <c r="BI46" s="22">
-        <f>[1]Annual!G242</f>
         <v>13.517547003711798</v>
       </c>
       <c r="BJ46" s="22">
-        <f>[1]Annual!H242</f>
         <v>13.361249107154258</v>
       </c>
       <c r="BK46" s="22">
-        <f>[1]Annual!I242</f>
         <v>13.606507617620867</v>
       </c>
       <c r="BL46" s="22">
-        <f>[1]Annual!J242</f>
         <v>14.516074757952453</v>
       </c>
       <c r="BM46" s="22">
-        <f>[1]Annual!K242</f>
         <v>14.540213315121395</v>
       </c>
       <c r="BN46" s="22">
-        <f>[1]Annual!L242</f>
         <v>13.74886505253429</v>
       </c>
       <c r="BO46" s="22">
-        <f>[1]Annual!M242</f>
         <v>14.095735151513274</v>
       </c>
       <c r="BP46" s="22">
-        <f>[1]Annual!N242</f>
         <v>13.095807011041332</v>
       </c>
       <c r="BQ46" s="22">
-        <f>[1]Annual!O242</f>
         <v>12.473425104248347</v>
       </c>
       <c r="BR46" s="22">
-        <f>[1]Annual!P242</f>
         <v>12.271681620873787</v>
       </c>
       <c r="BS46" s="22">
-        <f>[1]Annual!Q242</f>
         <v>10.996499155011534</v>
       </c>
       <c r="BT46" s="22">
-        <f>[1]Annual!R242</f>
         <v>10.205125532473266</v>
       </c>
       <c r="BU46" s="22">
-        <f>[1]Annual!S242</f>
         <v>10.182954131656141</v>
       </c>
       <c r="BV46" s="26">
-        <f>[1]Annual!T242</f>
         <v>9.6501403580565963</v>
       </c>
       <c r="BW46" s="26">
-        <f>[1]Annual!U242</f>
         <v>8.8203237471017513</v>
       </c>
       <c r="BX46" s="34">
-        <f>[1]Annual!V242</f>
         <v>10.185311031910887</v>
       </c>
       <c r="BY46" s="34">
-        <f>[1]Annual!W242</f>
         <v>10.069164020582223</v>
       </c>
       <c r="BZ46" s="34">
-        <f>[1]Annual!X242</f>
         <v>9.5517680442350059</v>
       </c>
       <c r="CA46" s="34">
-        <f>[1]Annual!Y242</f>
         <v>9.4003665287935068</v>
       </c>
       <c r="CB46" s="34">
-        <f>[1]Annual!Z242</f>
-        <v>9.0825267848195104</v>
+        <v>9.0872957602006306</v>
       </c>
       <c r="CC46" s="34">
-        <f>[1]Annual!AA242</f>
-        <v>8.5933977301849627</v>
+        <v>8.5917098442669051</v>
       </c>
     </row>
     <row r="47" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -20080,108 +17850,82 @@
         <v>33.550708247581326</v>
       </c>
       <c r="BD47" s="22">
-        <f>[1]Annual!B243</f>
         <v>34.975284768820643</v>
       </c>
       <c r="BE47" s="22">
-        <f>[1]Annual!C243</f>
         <v>34.897615258091172</v>
       </c>
       <c r="BF47" s="22">
-        <f>[1]Annual!D243</f>
         <v>34.783435262726613</v>
       </c>
       <c r="BG47" s="22">
-        <f>[1]Annual!E243</f>
         <v>34.540564030770057</v>
       </c>
       <c r="BH47" s="22">
-        <f>[1]Annual!F243</f>
         <v>33.618696206357839</v>
       </c>
       <c r="BI47" s="22">
-        <f>[1]Annual!G243</f>
         <v>33.813676305752217</v>
       </c>
       <c r="BJ47" s="22">
-        <f>[1]Annual!H243</f>
         <v>33.462585330073786</v>
       </c>
       <c r="BK47" s="22">
-        <f>[1]Annual!I243</f>
         <v>33.000860933008447</v>
       </c>
       <c r="BL47" s="22">
-        <f>[1]Annual!J243</f>
         <v>32.765288410901569</v>
       </c>
       <c r="BM47" s="22">
-        <f>[1]Annual!K243</f>
         <v>31.522542681533483</v>
       </c>
       <c r="BN47" s="22">
-        <f>[1]Annual!L243</f>
         <v>32.339556045623688</v>
       </c>
       <c r="BO47" s="22">
-        <f>[1]Annual!M243</f>
         <v>31.338682782695642</v>
       </c>
       <c r="BP47" s="22">
-        <f>[1]Annual!N243</f>
         <v>31.399493363390608</v>
       </c>
       <c r="BQ47" s="22">
-        <f>[1]Annual!O243</f>
         <v>30.775446631641834</v>
       </c>
       <c r="BR47" s="22">
-        <f>[1]Annual!P243</f>
         <v>31.047444475024015</v>
       </c>
       <c r="BS47" s="22">
-        <f>[1]Annual!Q243</f>
         <v>30.481950983722022</v>
       </c>
       <c r="BT47" s="22">
-        <f>[1]Annual!R243</f>
         <v>30.285917167213672</v>
       </c>
       <c r="BU47" s="22">
-        <f>[1]Annual!S243</f>
         <v>30.126550576900929</v>
       </c>
       <c r="BV47" s="26">
-        <f>[1]Annual!T243</f>
         <v>30.563740154978003</v>
       </c>
       <c r="BW47" s="26">
-        <f>[1]Annual!U243</f>
         <v>30.327507879516236</v>
       </c>
       <c r="BX47" s="34">
-        <f>[1]Annual!V243</f>
         <v>28.399917585046552</v>
       </c>
       <c r="BY47" s="34">
-        <f>[1]Annual!W243</f>
         <v>28.88980911837572</v>
       </c>
       <c r="BZ47" s="34">
-        <f>[1]Annual!X243</f>
         <v>29.221239936645727</v>
       </c>
       <c r="CA47" s="34">
-        <f>[1]Annual!Y243</f>
         <v>28.197622509066207</v>
       </c>
       <c r="CB47" s="34">
-        <f>[1]Annual!Z243</f>
-        <v>27.693977993152359</v>
+        <v>27.684918670717966</v>
       </c>
       <c r="CC47" s="34">
-        <f>[1]Annual!AA243</f>
-        <v>26.948683030678254</v>
+        <v>26.989765369349982</v>
       </c>
     </row>
     <row r="48" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -20351,108 +18095,82 @@
         <v>51.25493633352022</v>
       </c>
       <c r="BD48" s="22">
-        <f>[1]Annual!B248</f>
         <v>51.083620020564105</v>
       </c>
       <c r="BE48" s="22">
-        <f>[1]Annual!C248</f>
         <v>51.799575438290468</v>
       </c>
       <c r="BF48" s="22">
-        <f>[1]Annual!D248</f>
         <v>51.768151322109588</v>
       </c>
       <c r="BG48" s="22">
-        <f>[1]Annual!E248</f>
         <v>52.308488306780653</v>
       </c>
       <c r="BH48" s="22">
-        <f>[1]Annual!F248</f>
         <v>52.396900102825917</v>
       </c>
       <c r="BI48" s="22">
-        <f>[1]Annual!G248</f>
         <v>52.668776690535992</v>
       </c>
       <c r="BJ48" s="22">
-        <f>[1]Annual!H248</f>
         <v>53.176165562771956</v>
       </c>
       <c r="BK48" s="22">
-        <f>[1]Annual!I248</f>
         <v>53.392631449370697</v>
       </c>
       <c r="BL48" s="22">
-        <f>[1]Annual!J248</f>
         <v>52.718636831145972</v>
       </c>
       <c r="BM48" s="22">
-        <f>[1]Annual!K248</f>
         <v>53.937244003345121</v>
       </c>
       <c r="BN48" s="22">
-        <f>[1]Annual!L248</f>
         <v>53.91157890184202</v>
       </c>
       <c r="BO48" s="22">
-        <f>[1]Annual!M248</f>
         <v>54.565582065791084</v>
       </c>
       <c r="BP48" s="22">
-        <f>[1]Annual!N248</f>
         <v>55.504699625568065</v>
       </c>
       <c r="BQ48" s="22">
-        <f>[1]Annual!O248</f>
         <v>56.751128264109816</v>
       </c>
       <c r="BR48" s="22">
-        <f>[1]Annual!P248</f>
         <v>56.680873904102199</v>
       </c>
       <c r="BS48" s="22">
-        <f>[1]Annual!Q248</f>
         <v>58.521549861266443</v>
       </c>
       <c r="BT48" s="22">
-        <f>[1]Annual!R248</f>
         <v>59.508957300313057</v>
       </c>
       <c r="BU48" s="22">
-        <f>[1]Annual!S248</f>
         <v>59.690495291442936</v>
       </c>
       <c r="BV48" s="26">
-        <f>[1]Annual!T248</f>
         <v>59.786119486965397</v>
       </c>
       <c r="BW48" s="26">
-        <f>[1]Annual!U248</f>
         <v>60.852168373382007</v>
       </c>
       <c r="BX48" s="34">
-        <f>[1]Annual!V248</f>
         <v>61.414771383042556</v>
       </c>
       <c r="BY48" s="34">
-        <f>[1]Annual!W248</f>
         <v>61.041026861042056</v>
       </c>
       <c r="BZ48" s="34">
-        <f>[1]Annual!X248</f>
         <v>61.226992019119265</v>
       </c>
       <c r="CA48" s="34">
-        <f>[1]Annual!Y248</f>
         <v>62.402010962140274</v>
       </c>
       <c r="CB48" s="34">
-        <f>[1]Annual!Z248</f>
-        <v>63.223495222028149</v>
+        <v>63.227785569081405</v>
       </c>
       <c r="CC48" s="34">
-        <f>[1]Annual!AA248</f>
-        <v>64.457919239136785</v>
+        <v>64.418524786383117</v>
       </c>
     </row>
     <row r="49" spans="1:81" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -20705,107 +18423,81 @@
         <v>100</v>
       </c>
       <c r="BD50" s="32">
-        <f>[1]Annual!B261</f>
         <v>100</v>
       </c>
       <c r="BE50" s="32">
-        <f>[1]Annual!C261</f>
         <v>100</v>
       </c>
       <c r="BF50" s="32">
-        <f>[1]Annual!D261</f>
         <v>100</v>
       </c>
       <c r="BG50" s="32">
-        <f>[1]Annual!E261</f>
         <v>100</v>
       </c>
       <c r="BH50" s="32">
-        <f>[1]Annual!F261</f>
         <v>100</v>
       </c>
       <c r="BI50" s="32">
-        <f>[1]Annual!G261</f>
         <v>100</v>
       </c>
       <c r="BJ50" s="32">
-        <f>[1]Annual!H261</f>
         <v>100</v>
       </c>
       <c r="BK50" s="32">
-        <f>[1]Annual!I261</f>
         <v>100</v>
       </c>
       <c r="BL50" s="32">
-        <f>[1]Annual!J261</f>
         <v>100</v>
       </c>
       <c r="BM50" s="32">
-        <f>[1]Annual!K261</f>
         <v>100</v>
       </c>
       <c r="BN50" s="32">
-        <f>[1]Annual!L261</f>
         <v>100</v>
       </c>
       <c r="BO50" s="32">
-        <f>[1]Annual!M261</f>
         <v>100</v>
       </c>
       <c r="BP50" s="32">
-        <f>[1]Annual!N261</f>
         <v>100</v>
       </c>
       <c r="BQ50" s="32">
-        <f>[1]Annual!O261</f>
         <v>100</v>
       </c>
       <c r="BR50" s="32">
-        <f>[1]Annual!P261</f>
         <v>100</v>
       </c>
       <c r="BS50" s="32">
-        <f>[1]Annual!Q261</f>
         <v>100</v>
       </c>
       <c r="BT50" s="32">
-        <f>[1]Annual!R261</f>
         <v>100</v>
       </c>
       <c r="BU50" s="32">
-        <f>[1]Annual!S261</f>
         <v>100</v>
       </c>
       <c r="BV50" s="27">
-        <f>[1]Annual!T261</f>
         <v>100</v>
       </c>
       <c r="BW50" s="27">
-        <f>[1]Annual!U261</f>
         <v>100</v>
       </c>
       <c r="BX50" s="27">
-        <f>[1]Annual!V261</f>
         <v>100</v>
       </c>
       <c r="BY50" s="27">
-        <f>[1]Annual!W261</f>
         <v>100</v>
       </c>
       <c r="BZ50" s="27">
-        <f>[1]Annual!X261</f>
         <v>100</v>
       </c>
       <c r="CA50" s="27">
-        <f>[1]Annual!Y261</f>
         <v>100</v>
       </c>
       <c r="CB50" s="27">
-        <f>[1]Annual!Z261</f>
         <v>100</v>
       </c>
       <c r="CC50" s="27">
-        <f>[1]Annual!AA261</f>
         <v>100</v>
       </c>
     </row>
@@ -21660,9 +19352,8 @@
       </c>
     </row>
     <row r="3" spans="1:81" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="str">
-        <f>Current_2018based!$A$3</f>
-        <v>As of January 2026</v>
+      <c r="A3" s="14" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:81" x14ac:dyDescent="0.2">
@@ -22099,108 +19790,82 @@
         <v>1029173.6330228868</v>
       </c>
       <c r="BD10" s="19">
-        <f>[1]Annual!B127</f>
         <v>1064005.0869465019</v>
       </c>
       <c r="BE10" s="19">
-        <f>[1]Annual!C127</f>
         <v>1105117.4866392382</v>
       </c>
       <c r="BF10" s="19">
-        <f>[1]Annual!D127</f>
         <v>1144990.5954578116</v>
       </c>
       <c r="BG10" s="19">
-        <f>[1]Annual!E127</f>
         <v>1197371.0373716741</v>
       </c>
       <c r="BH10" s="19">
-        <f>[1]Annual!F127</f>
         <v>1257109.2132941873</v>
       </c>
       <c r="BI10" s="19">
-        <f>[1]Annual!G127</f>
         <v>1301069.2243305743</v>
       </c>
       <c r="BJ10" s="19">
-        <f>[1]Annual!H127</f>
         <v>1360678.1688071573</v>
       </c>
       <c r="BK10" s="19">
-        <f>[1]Annual!I127</f>
         <v>1433746.8087559578</v>
       </c>
       <c r="BL10" s="19">
-        <f>[1]Annual!J127</f>
         <v>1482351.7473987523</v>
       </c>
       <c r="BM10" s="19">
-        <f>[1]Annual!K127</f>
         <v>1480206.8239089095</v>
       </c>
       <c r="BN10" s="19">
-        <f>[1]Annual!L127</f>
         <v>1499800.7696724271</v>
       </c>
       <c r="BO10" s="19">
-        <f>[1]Annual!M127</f>
         <v>1550555.2016332422</v>
       </c>
       <c r="BP10" s="19">
-        <f>[1]Annual!N127</f>
         <v>1598311.5075543907</v>
       </c>
       <c r="BQ10" s="19">
-        <f>[1]Annual!O127</f>
         <v>1645191.6850298091</v>
       </c>
       <c r="BR10" s="19">
-        <f>[1]Annual!P127</f>
         <v>1676006.3550526681</v>
       </c>
       <c r="BS10" s="19">
-        <f>[1]Annual!Q127</f>
         <v>1688343.7557025508</v>
       </c>
       <c r="BT10" s="19">
-        <f>[1]Annual!R127</f>
         <v>1672084.9828823139</v>
       </c>
       <c r="BU10" s="19">
-        <f>[1]Annual!S127</f>
         <v>1743134.2940204137</v>
       </c>
       <c r="BV10" s="19">
-        <f>[1]Annual!T127</f>
         <v>1762616.4965786885</v>
       </c>
       <c r="BW10" s="19">
-        <f>[1]Annual!U127</f>
         <v>1783855.1472581751</v>
       </c>
       <c r="BX10" s="19">
-        <f>[1]Annual!V127</f>
         <v>1780390.5640921537</v>
       </c>
       <c r="BY10" s="19">
-        <f>[1]Annual!W127</f>
         <v>1775210.3171187984</v>
       </c>
       <c r="BZ10" s="19">
-        <f>[1]Annual!X127</f>
         <v>1783734.6554432954</v>
       </c>
       <c r="CA10" s="19">
-        <f>[1]Annual!Y127</f>
         <v>1805216.771038763</v>
       </c>
       <c r="CB10" s="19">
-        <f>[1]Annual!Z127</f>
-        <v>1778234.5329187952</v>
+        <v>1777999.1647256417</v>
       </c>
       <c r="CC10" s="19">
-        <f>[1]Annual!AA127</f>
-        <v>1833110.7044894486</v>
+        <v>1832888.2952783871</v>
       </c>
     </row>
     <row r="11" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -22370,108 +20035,82 @@
         <v>2094359.3252327673</v>
       </c>
       <c r="BD11" s="19">
-        <f>[1]Annual!B128</f>
         <v>2233331.908558073</v>
       </c>
       <c r="BE11" s="19">
-        <f>[1]Annual!C128</f>
         <v>2263212.7783727339</v>
       </c>
       <c r="BF11" s="19">
-        <f>[1]Annual!D128</f>
         <v>2346382.7963735494</v>
       </c>
       <c r="BG11" s="19">
-        <f>[1]Annual!E128</f>
         <v>2462870.600499433</v>
       </c>
       <c r="BH11" s="19">
-        <f>[1]Annual!F128</f>
         <v>2571406.3345832815</v>
       </c>
       <c r="BI11" s="19">
-        <f>[1]Annual!G128</f>
         <v>2701284.7496357504</v>
       </c>
       <c r="BJ11" s="19">
-        <f>[1]Annual!H128</f>
         <v>2802098.6329476382</v>
       </c>
       <c r="BK11" s="19">
-        <f>[1]Annual!I128</f>
         <v>2940674.679845708</v>
       </c>
       <c r="BL11" s="19">
-        <f>[1]Annual!J128</f>
         <v>3101573.6524675926</v>
       </c>
       <c r="BM11" s="19">
-        <f>[1]Annual!K128</f>
         <v>3057652.2915348206</v>
       </c>
       <c r="BN11" s="19">
-        <f>[1]Annual!L128</f>
         <v>3358023.2875841749</v>
       </c>
       <c r="BO11" s="19">
-        <f>[1]Annual!M128</f>
         <v>3411809.2007066575</v>
       </c>
       <c r="BP11" s="19">
-        <f>[1]Annual!N128</f>
         <v>3674109.760798207</v>
       </c>
       <c r="BQ11" s="19">
-        <f>[1]Annual!O128</f>
         <v>3924518.7466281406</v>
       </c>
       <c r="BR11" s="19">
-        <f>[1]Annual!P128</f>
         <v>4218871.831168456</v>
       </c>
       <c r="BS11" s="19">
-        <f>[1]Annual!Q128</f>
         <v>4493389.9589908756</v>
       </c>
       <c r="BT11" s="19">
-        <f>[1]Annual!R128</f>
         <v>4861341.7522844896</v>
       </c>
       <c r="BU11" s="19">
-        <f>[1]Annual!S128</f>
         <v>5202581.5831372812</v>
       </c>
       <c r="BV11" s="19">
-        <f>[1]Annual!T128</f>
         <v>5582525.2893169122</v>
       </c>
       <c r="BW11" s="19">
-        <f>[1]Annual!U128</f>
         <v>5887868.6968866978</v>
       </c>
       <c r="BX11" s="19">
-        <f>[1]Annual!V128</f>
         <v>5115315.7129913447</v>
       </c>
       <c r="BY11" s="19">
-        <f>[1]Annual!W128</f>
         <v>5551621.8662187792</v>
       </c>
       <c r="BZ11" s="19">
-        <f>[1]Annual!X128</f>
         <v>5913747.6649654768</v>
       </c>
       <c r="CA11" s="19">
-        <f>[1]Annual!Y128</f>
         <v>6128235.4957260517</v>
       </c>
       <c r="CB11" s="19">
-        <f>[1]Annual!Z128</f>
-        <v>6473862.2736754334</v>
+        <v>6473231.8286454566</v>
       </c>
       <c r="CC11" s="19">
-        <f>[1]Annual!AA128</f>
-        <v>6572519.1983347684</v>
+        <v>6583687.4878399381</v>
       </c>
     </row>
     <row r="12" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -22641,108 +20280,82 @@
         <v>3568568.5965783703</v>
       </c>
       <c r="BD12" s="19">
-        <f>[1]Annual!B133</f>
         <v>3688046.2446433334</v>
       </c>
       <c r="BE12" s="19">
-        <f>[1]Annual!C133</f>
         <v>3830053.4704007208</v>
       </c>
       <c r="BF12" s="19">
-        <f>[1]Annual!D133</f>
         <v>3974520.639199873</v>
       </c>
       <c r="BG12" s="19">
-        <f>[1]Annual!E133</f>
         <v>4185435.7878863006</v>
       </c>
       <c r="BH12" s="19">
-        <f>[1]Annual!F133</f>
         <v>4532562.3563551698</v>
       </c>
       <c r="BI12" s="19">
-        <f>[1]Annual!G133</f>
         <v>4771970.6335892519</v>
       </c>
       <c r="BJ12" s="19">
-        <f>[1]Annual!H133</f>
         <v>5078027.4752690587</v>
       </c>
       <c r="BK12" s="19">
-        <f>[1]Annual!I133</f>
         <v>5468817.7608404998</v>
       </c>
       <c r="BL12" s="19">
-        <f>[1]Annual!J133</f>
         <v>5686952.1291571362</v>
       </c>
       <c r="BM12" s="19">
-        <f>[1]Annual!K133</f>
         <v>5881773.9015875971</v>
       </c>
       <c r="BN12" s="19">
-        <f>[1]Annual!L133</f>
         <v>6326036.9392845146</v>
       </c>
       <c r="BO12" s="19">
-        <f>[1]Annual!M133</f>
         <v>6652995.9905493334</v>
       </c>
       <c r="BP12" s="19">
-        <f>[1]Annual!N133</f>
         <v>7144044.9218433676</v>
       </c>
       <c r="BQ12" s="19">
-        <f>[1]Annual!O133</f>
         <v>7684933.195281975</v>
       </c>
       <c r="BR12" s="19">
-        <f>[1]Annual!P133</f>
         <v>8201168.5590072311</v>
       </c>
       <c r="BS12" s="19">
-        <f>[1]Annual!Q133</f>
         <v>8809173.7357357219</v>
       </c>
       <c r="BT12" s="19">
-        <f>[1]Annual!R133</f>
         <v>9529249.1598030627</v>
       </c>
       <c r="BU12" s="19">
-        <f>[1]Annual!S133</f>
         <v>10230262.208913909</v>
       </c>
       <c r="BV12" s="19">
-        <f>[1]Annual!T133</f>
         <v>10920048.472266145</v>
       </c>
       <c r="BW12" s="19">
-        <f>[1]Annual!U133</f>
         <v>11711026.767278373</v>
       </c>
       <c r="BX12" s="19">
-        <f>[1]Annual!V133</f>
         <v>10642137.002289824</v>
       </c>
       <c r="BY12" s="19">
-        <f>[1]Annual!W133</f>
         <v>11213252.036594167</v>
       </c>
       <c r="BZ12" s="19">
-        <f>[1]Annual!X133</f>
         <v>12248122.370699735</v>
       </c>
       <c r="CA12" s="19">
-        <f>[1]Annual!Y133</f>
         <v>13112940.310321592</v>
       </c>
       <c r="CB12" s="19">
-        <f>[1]Annual!Z133</f>
-        <v>13992259.830376996</v>
+        <v>13997909.306186138</v>
       </c>
       <c r="CC12" s="19">
-        <f>[1]Annual!AA133</f>
-        <v>14818232.355490401</v>
+        <v>14812061.022104058</v>
       </c>
     </row>
     <row r="13" spans="1:81" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -22995,108 +20608,82 @@
         <v>6692101.554834025</v>
       </c>
       <c r="BD14" s="24">
-        <f>[1]Annual!B146</f>
         <v>6985383.2401479082</v>
       </c>
       <c r="BE14" s="24">
-        <f>[1]Annual!C146</f>
         <v>7198383.7354126927</v>
       </c>
       <c r="BF14" s="24">
-        <f>[1]Annual!D146</f>
         <v>7465894.0310312342</v>
       </c>
       <c r="BG14" s="24">
-        <f>[1]Annual!E146</f>
         <v>7845677.4257574081</v>
       </c>
       <c r="BH14" s="24">
-        <f>[1]Annual!F146</f>
         <v>8361077.9042326389</v>
       </c>
       <c r="BI14" s="24">
-        <f>[1]Annual!G146</f>
         <v>8774324.6075555757</v>
       </c>
       <c r="BJ14" s="24">
-        <f>[1]Annual!H146</f>
         <v>9240804.2770238537</v>
       </c>
       <c r="BK14" s="24">
-        <f>[1]Annual!I146</f>
         <v>9843239.2494421657</v>
       </c>
       <c r="BL14" s="24">
-        <f>[1]Annual!J146</f>
         <v>10270877.52902348</v>
       </c>
       <c r="BM14" s="24">
-        <f>[1]Annual!K146</f>
         <v>10419633.017031327</v>
       </c>
       <c r="BN14" s="24">
-        <f>[1]Annual!L146</f>
         <v>11183860.996541116</v>
       </c>
       <c r="BO14" s="24">
-        <f>[1]Annual!M146</f>
         <v>11615360.392889233</v>
       </c>
       <c r="BP14" s="24">
-        <f>[1]Annual!N146</f>
         <v>12416466.190195967</v>
       </c>
       <c r="BQ14" s="24">
-        <f>[1]Annual!O146</f>
         <v>13254643.626939924</v>
       </c>
       <c r="BR14" s="24">
-        <f>[1]Annual!P146</f>
         <v>14096046.745228356</v>
       </c>
       <c r="BS14" s="24">
-        <f>[1]Annual!Q146</f>
         <v>14990907.450429149</v>
       </c>
       <c r="BT14" s="24">
-        <f>[1]Annual!R146</f>
         <v>16062675.894969866</v>
       </c>
       <c r="BU14" s="36">
-        <f>[1]Annual!S146</f>
         <v>17175978.086071603</v>
       </c>
       <c r="BV14" s="36">
-        <f>[1]Annual!T146</f>
         <v>18265190.258161746</v>
       </c>
       <c r="BW14" s="36">
-        <f>[1]Annual!U146</f>
         <v>19382750.611423247</v>
       </c>
       <c r="BX14" s="24">
-        <f>[1]Annual!V146</f>
         <v>17537843.279373322</v>
       </c>
       <c r="BY14" s="24">
-        <f>[1]Annual!W146</f>
         <v>18540084.219931744</v>
       </c>
       <c r="BZ14" s="24">
-        <f>[1]Annual!X146</f>
         <v>19945604.69110851</v>
       </c>
       <c r="CA14" s="24">
-        <f>[1]Annual!Y146</f>
         <v>21046392.577086408</v>
       </c>
       <c r="CB14" s="24">
-        <f>[1]Annual!Z146</f>
-        <v>22244356.636971224</v>
+        <v>22249140.299557235</v>
       </c>
       <c r="CC14" s="24">
-        <f>[1]Annual!AA146</f>
-        <v>23223862.258314617</v>
+        <v>23228636.805222385</v>
       </c>
     </row>
     <row r="15" spans="1:81" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -23586,9 +21173,8 @@
       <c r="CC20" s="19"/>
     </row>
     <row r="21" spans="1:81" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="str">
-        <f>$A$3</f>
-        <v>As of January 2026</v>
+      <c r="A21" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
@@ -24094,321 +21680,242 @@
       <c r="A27" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="28" t="str">
-        <f>Current_2018based!B27</f>
-        <v>1946 - 1947</v>
-      </c>
-      <c r="C27" s="28" t="str">
-        <f>Current_2018based!C27</f>
-        <v>1947 - 1948</v>
-      </c>
-      <c r="D27" s="28" t="str">
-        <f>Current_2018based!D27</f>
-        <v>1948 - 1949</v>
-      </c>
-      <c r="E27" s="28" t="str">
-        <f>Current_2018based!E27</f>
-        <v>1949 - 1950</v>
-      </c>
-      <c r="F27" s="28" t="str">
-        <f>Current_2018based!F27</f>
-        <v>1950 - 1951</v>
-      </c>
-      <c r="G27" s="28" t="str">
-        <f>Current_2018based!G27</f>
-        <v>1951 - 1952</v>
-      </c>
-      <c r="H27" s="28" t="str">
-        <f>Current_2018based!H27</f>
-        <v>1952 - 1953</v>
-      </c>
-      <c r="I27" s="28" t="str">
-        <f>Current_2018based!I27</f>
-        <v>1953 - 1954</v>
-      </c>
-      <c r="J27" s="28" t="str">
-        <f>Current_2018based!J27</f>
-        <v>1954 - 1955</v>
-      </c>
-      <c r="K27" s="28" t="str">
-        <f>Current_2018based!K27</f>
-        <v>1955 - 1956</v>
-      </c>
-      <c r="L27" s="28" t="str">
-        <f>Current_2018based!L27</f>
-        <v>1956 - 1957</v>
-      </c>
-      <c r="M27" s="28" t="str">
-        <f>Current_2018based!M27</f>
-        <v>1957 - 1958</v>
-      </c>
-      <c r="N27" s="28" t="str">
-        <f>Current_2018based!N27</f>
-        <v>1958 - 1959</v>
-      </c>
-      <c r="O27" s="28" t="str">
-        <f>Current_2018based!O27</f>
-        <v>1959 - 1960</v>
-      </c>
-      <c r="P27" s="28" t="str">
-        <f>Current_2018based!P27</f>
-        <v>1960 - 1961</v>
-      </c>
-      <c r="Q27" s="28" t="str">
-        <f>Current_2018based!Q27</f>
-        <v>1961 - 1962</v>
-      </c>
-      <c r="R27" s="28" t="str">
-        <f>Current_2018based!R27</f>
-        <v>1962 - 1963</v>
-      </c>
-      <c r="S27" s="28" t="str">
-        <f>Current_2018based!S27</f>
-        <v>1963 - 1964</v>
-      </c>
-      <c r="T27" s="28" t="str">
-        <f>Current_2018based!T27</f>
-        <v>1964 - 1965</v>
-      </c>
-      <c r="U27" s="28" t="str">
-        <f>Current_2018based!U27</f>
-        <v>1965 - 1966</v>
-      </c>
-      <c r="V27" s="28" t="str">
-        <f>Current_2018based!V27</f>
-        <v>1966 - 1967</v>
-      </c>
-      <c r="W27" s="28" t="str">
-        <f>Current_2018based!W27</f>
-        <v>1967 - 1968</v>
-      </c>
-      <c r="X27" s="28" t="str">
-        <f>Current_2018based!X27</f>
-        <v>1968 - 1969</v>
-      </c>
-      <c r="Y27" s="28" t="str">
-        <f>Current_2018based!Y27</f>
-        <v>1969 - 1970</v>
-      </c>
-      <c r="Z27" s="28" t="str">
-        <f>Current_2018based!Z27</f>
-        <v>1970 - 1971</v>
-      </c>
-      <c r="AA27" s="28" t="str">
-        <f>Current_2018based!AA27</f>
-        <v>1971 - 1972</v>
-      </c>
-      <c r="AB27" s="28" t="str">
-        <f>Current_2018based!AB27</f>
-        <v>1972 - 1973</v>
-      </c>
-      <c r="AC27" s="28" t="str">
-        <f>Current_2018based!AC27</f>
-        <v>1973 - 1974</v>
-      </c>
-      <c r="AD27" s="28" t="str">
-        <f>Current_2018based!AD27</f>
-        <v>1974 - 1975</v>
-      </c>
-      <c r="AE27" s="28" t="str">
-        <f>Current_2018based!AE27</f>
-        <v>1975 - 1976</v>
-      </c>
-      <c r="AF27" s="28" t="str">
-        <f>Current_2018based!AF27</f>
-        <v>1976 - 1977</v>
-      </c>
-      <c r="AG27" s="28" t="str">
-        <f>Current_2018based!AG27</f>
-        <v>1977 - 1978</v>
-      </c>
-      <c r="AH27" s="28" t="str">
-        <f>Current_2018based!AH27</f>
-        <v>1978 - 1979</v>
-      </c>
-      <c r="AI27" s="28" t="str">
-        <f>Current_2018based!AI27</f>
-        <v>1979 - 1980</v>
-      </c>
-      <c r="AJ27" s="28" t="str">
-        <f>Current_2018based!AJ27</f>
-        <v>1980 - 1981</v>
-      </c>
-      <c r="AK27" s="28" t="str">
-        <f>Current_2018based!AK27</f>
-        <v>1981 - 1982</v>
-      </c>
-      <c r="AL27" s="28" t="str">
-        <f>Current_2018based!AL27</f>
-        <v>1982 - 1983</v>
-      </c>
-      <c r="AM27" s="28" t="str">
-        <f>Current_2018based!AM27</f>
-        <v>1983 - 1984</v>
-      </c>
-      <c r="AN27" s="28" t="str">
-        <f>Current_2018based!AN27</f>
-        <v>1984 - 1985</v>
-      </c>
-      <c r="AO27" s="28" t="str">
-        <f>Current_2018based!AO27</f>
-        <v>1985 - 1986</v>
-      </c>
-      <c r="AP27" s="28" t="str">
-        <f>Current_2018based!AP27</f>
-        <v>1986 - 1987</v>
-      </c>
-      <c r="AQ27" s="28" t="str">
-        <f>Current_2018based!AQ27</f>
-        <v>1987- 1988</v>
-      </c>
-      <c r="AR27" s="28" t="str">
-        <f>Current_2018based!AR27</f>
-        <v>1988 - 1989</v>
-      </c>
-      <c r="AS27" s="28" t="str">
-        <f>Current_2018based!AS27</f>
-        <v>1989 - 1990</v>
-      </c>
-      <c r="AT27" s="28" t="str">
-        <f>Current_2018based!AT27</f>
-        <v>1990 - 1991</v>
-      </c>
-      <c r="AU27" s="28" t="str">
-        <f>Current_2018based!AU27</f>
-        <v>1991 - 1992</v>
-      </c>
-      <c r="AV27" s="28" t="str">
-        <f>Current_2018based!AV27</f>
-        <v>1992 - 1993</v>
-      </c>
-      <c r="AW27" s="28" t="str">
-        <f>Current_2018based!AW27</f>
-        <v>1993 - 1994</v>
-      </c>
-      <c r="AX27" s="28" t="str">
-        <f>Current_2018based!AX27</f>
-        <v>1994 - 1995</v>
-      </c>
-      <c r="AY27" s="28" t="str">
-        <f>Current_2018based!AY27</f>
-        <v>1995 - 1996</v>
-      </c>
-      <c r="AZ27" s="28" t="str">
-        <f>Current_2018based!AZ27</f>
-        <v>1996 - 1997</v>
-      </c>
-      <c r="BA27" s="28" t="str">
-        <f>Current_2018based!BA27</f>
-        <v>1997 - 1998</v>
-      </c>
-      <c r="BB27" s="28" t="str">
-        <f>Current_2018based!BB27</f>
-        <v>1998 - 1999</v>
-      </c>
-      <c r="BC27" s="28" t="str">
-        <f>Current_2018based!BC27</f>
-        <v>1999 - 2000</v>
-      </c>
-      <c r="BD27" s="28" t="str">
-        <f>Current_2018based!BD27</f>
-        <v>2000 - 2001</v>
-      </c>
-      <c r="BE27" s="28" t="str">
-        <f>Current_2018based!BE27</f>
-        <v>2001 - 2002</v>
-      </c>
-      <c r="BF27" s="28" t="str">
-        <f>Current_2018based!BF27</f>
-        <v>2002 - 2003</v>
-      </c>
-      <c r="BG27" s="28" t="str">
-        <f>Current_2018based!BG27</f>
-        <v>2003 - 2004</v>
-      </c>
-      <c r="BH27" s="28" t="str">
-        <f>Current_2018based!BH27</f>
-        <v>2004 - 2005</v>
-      </c>
-      <c r="BI27" s="28" t="str">
-        <f>Current_2018based!BI27</f>
-        <v>2005 - 2006</v>
-      </c>
-      <c r="BJ27" s="28" t="str">
-        <f>Current_2018based!BJ27</f>
-        <v>2006 - 2007</v>
-      </c>
-      <c r="BK27" s="28" t="str">
-        <f>Current_2018based!BK27</f>
-        <v>2007 - 2008</v>
-      </c>
-      <c r="BL27" s="28" t="str">
-        <f>Current_2018based!BL27</f>
-        <v>2008 - 2009</v>
-      </c>
-      <c r="BM27" s="28" t="str">
-        <f>Current_2018based!BM27</f>
-        <v>2009 - 2010</v>
-      </c>
-      <c r="BN27" s="28" t="str">
-        <f>Current_2018based!BN27</f>
-        <v>2010 - 2011</v>
-      </c>
-      <c r="BO27" s="28" t="str">
-        <f>Current_2018based!BO27</f>
-        <v>2011 - 2012</v>
-      </c>
-      <c r="BP27" s="28" t="str">
-        <f>Current_2018based!BP27</f>
-        <v>2012 - 2013</v>
-      </c>
-      <c r="BQ27" s="28" t="str">
-        <f>Current_2018based!BQ27</f>
-        <v>2013 - 2014</v>
-      </c>
-      <c r="BR27" s="28" t="str">
-        <f>Current_2018based!BR27</f>
-        <v>2014 - 2015</v>
-      </c>
-      <c r="BS27" s="28" t="str">
-        <f>Current_2018based!BS27</f>
-        <v>2015 - 2016</v>
-      </c>
-      <c r="BT27" s="28" t="str">
-        <f>Current_2018based!BT27</f>
-        <v>2016 - 2017</v>
-      </c>
-      <c r="BU27" s="28" t="str">
-        <f>Current_2018based!BU27</f>
-        <v>2017 - 2018</v>
-      </c>
-      <c r="BV27" s="28" t="str">
-        <f>Current_2018based!BV27</f>
-        <v>2018 - 2019</v>
-      </c>
-      <c r="BW27" s="28" t="str">
-        <f>Current_2018based!BW27</f>
-        <v>2019 - 2020</v>
-      </c>
-      <c r="BX27" s="28" t="str">
-        <f>Current_2018based!BX27</f>
-        <v>2020 - 2021</v>
-      </c>
-      <c r="BY27" s="28" t="str">
-        <f>Current_2018based!BY27</f>
-        <v>2021 - 2022</v>
-      </c>
-      <c r="BZ27" s="28" t="str">
-        <f>Current_2018based!BZ27</f>
-        <v>2022 - 2023</v>
-      </c>
-      <c r="CA27" s="28" t="str">
-        <f>Current_2018based!CA27</f>
-        <v>2023 - 2024</v>
-      </c>
-      <c r="CB27" s="28" t="str">
-        <f>Current_2018based!CB27</f>
-        <v>2024 - 2025</v>
+      <c r="B27" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="K27" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="M27" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="N27" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="O27" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="P27" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="R27" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S27" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="T27" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="U27" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="V27" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="W27" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="X27" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y27" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z27" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA27" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB27" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC27" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD27" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE27" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF27" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG27" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH27" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI27" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ27" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK27" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL27" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM27" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN27" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO27" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP27" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ27" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR27" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS27" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT27" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU27" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="AV27" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW27" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX27" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY27" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="AZ27" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="BA27" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB27" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC27" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD27" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="BE27" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="BF27" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG27" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH27" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="BI27" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="BJ27" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BK27" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="BL27" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="BM27" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="BN27" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="BO27" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="BP27" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="BQ27" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="BR27" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="BS27" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="BT27" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="BU27" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="BV27" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="BW27" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="BX27" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="BY27" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="BZ27" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="CA27" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="CB27" s="28" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -24578,104 +22085,79 @@
         <v>3.3844036318664479</v>
       </c>
       <c r="BD28" s="26">
-        <f>[1]Annual!B435</f>
         <v>3.8639288662351419</v>
       </c>
       <c r="BE28" s="26">
-        <f>[1]Annual!C435</f>
         <v>3.6080425204229698</v>
       </c>
       <c r="BF28" s="26">
-        <f>[1]Annual!D435</f>
         <v>4.5747486592166098</v>
       </c>
       <c r="BG28" s="26">
-        <f>[1]Annual!E435</f>
         <v>4.9891114832411034</v>
       </c>
       <c r="BH28" s="26">
-        <f>[1]Annual!F435</f>
         <v>3.4969126446215455</v>
       </c>
       <c r="BI28" s="26">
-        <f>[1]Annual!G435</f>
         <v>4.5815351990400757</v>
       </c>
       <c r="BJ28" s="26">
-        <f>[1]Annual!H435</f>
         <v>5.3700163362550484</v>
       </c>
       <c r="BK28" s="26">
-        <f>[1]Annual!I435</f>
         <v>3.3900642948923689</v>
       </c>
       <c r="BL28" s="26">
-        <f>[1]Annual!J435</f>
         <v>-0.14469733608144963</v>
       </c>
       <c r="BM28" s="26">
-        <f>[1]Annual!K435</f>
         <v>1.3237302684346588</v>
       </c>
       <c r="BN28" s="26">
-        <f>[1]Annual!L435</f>
         <v>3.3840782714027</v>
       </c>
       <c r="BO28" s="26">
-        <f>[1]Annual!M435</f>
         <v>3.0799487738872813</v>
       </c>
       <c r="BP28" s="26">
-        <f>[1]Annual!N435</f>
         <v>2.9331064222362357</v>
       </c>
       <c r="BQ28" s="26">
-        <f>[1]Annual!O435</f>
         <v>1.8730139656827163</v>
       </c>
       <c r="BR28" s="26">
-        <f>[1]Annual!P435</f>
         <v>0.73611896593881454</v>
       </c>
       <c r="BS28" s="26">
-        <f>[1]Annual!Q435</f>
         <v>-0.96300132987261122</v>
       </c>
       <c r="BT28" s="26">
-        <f>[1]Annual!R435</f>
         <v>4.2491447423698645</v>
       </c>
       <c r="BU28" s="26">
-        <f>[1]Annual!S435</f>
         <v>1.1176535637619054</v>
       </c>
       <c r="BV28" s="26">
-        <f>[1]Annual!T435</f>
         <v>1.204950181773043</v>
       </c>
       <c r="BW28" s="34">
-        <f>[1]Annual!U435</f>
         <v>-0.19421886196009552</v>
       </c>
       <c r="BX28" s="34">
-        <f>[1]Annual!V435</f>
         <v>-0.2909612687144687</v>
       </c>
       <c r="BY28" s="34">
-        <f>[1]Annual!W435</f>
         <v>0.48018751594077003</v>
       </c>
       <c r="BZ28" s="34">
-        <f>[1]Annual!X435</f>
         <v>1.2043335890745936</v>
       </c>
       <c r="CA28" s="34">
-        <f>[1]Annual!Y435</f>
-        <v>-1.4946813342777432</v>
+        <v>-1.5077195575498479</v>
       </c>
       <c r="CB28" s="34">
-        <f>[1]Annual!Z435</f>
-        <v>3.0859917831299555</v>
+        <v>3.0871291529102081</v>
       </c>
     </row>
     <row r="29" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -24845,104 +22327,79 @@
         <v>6.6355644120969828</v>
       </c>
       <c r="BD29" s="26">
-        <f>[1]Annual!B436</f>
         <v>1.3379502482438141</v>
       </c>
       <c r="BE29" s="26">
-        <f>[1]Annual!C436</f>
         <v>3.6748651649366906</v>
       </c>
       <c r="BF29" s="26">
-        <f>[1]Annual!D436</f>
         <v>4.9645694771510023</v>
       </c>
       <c r="BG29" s="26">
-        <f>[1]Annual!E436</f>
         <v>4.4068792758271229</v>
       </c>
       <c r="BH29" s="26">
-        <f>[1]Annual!F436</f>
         <v>5.0508709302653472</v>
       </c>
       <c r="BI29" s="26">
-        <f>[1]Annual!G436</f>
         <v>3.7320716864625894</v>
       </c>
       <c r="BJ29" s="26">
-        <f>[1]Annual!H436</f>
         <v>4.945437868198681</v>
       </c>
       <c r="BK29" s="26">
-        <f>[1]Annual!I436</f>
         <v>5.4714985552338078</v>
       </c>
       <c r="BL29" s="26">
-        <f>[1]Annual!J436</f>
         <v>-1.416099240391361</v>
       </c>
       <c r="BM29" s="26">
-        <f>[1]Annual!K436</f>
         <v>9.8235825205154299</v>
       </c>
       <c r="BN29" s="26">
-        <f>[1]Annual!L436</f>
         <v>1.6017135235883728</v>
       </c>
       <c r="BO29" s="26">
-        <f>[1]Annual!M436</f>
         <v>7.68801960078018</v>
       </c>
       <c r="BP29" s="26">
-        <f>[1]Annual!N436</f>
         <v>6.8155009548634666</v>
       </c>
       <c r="BQ29" s="26">
-        <f>[1]Annual!O436</f>
         <v>7.5003612810670575</v>
       </c>
       <c r="BR29" s="26">
-        <f>[1]Annual!P436</f>
         <v>6.5069084534475934</v>
       </c>
       <c r="BS29" s="26">
-        <f>[1]Annual!Q436</f>
         <v>8.1887349340195641</v>
       </c>
       <c r="BT29" s="26">
-        <f>[1]Annual!R436</f>
         <v>7.019457759628466</v>
       </c>
       <c r="BU29" s="26">
-        <f>[1]Annual!S436</f>
         <v>7.302984107180805</v>
       </c>
       <c r="BV29" s="26">
-        <f>[1]Annual!T436</f>
         <v>5.4696287387019993</v>
       </c>
       <c r="BW29" s="34">
-        <f>[1]Annual!U436</f>
         <v>-13.121097355718078</v>
       </c>
       <c r="BX29" s="34">
-        <f>[1]Annual!V436</f>
         <v>8.5294081090508342</v>
       </c>
       <c r="BY29" s="34">
-        <f>[1]Annual!W436</f>
         <v>6.5228829965925428</v>
       </c>
       <c r="BZ29" s="34">
-        <f>[1]Annual!X436</f>
         <v>3.6269357928687924</v>
       </c>
       <c r="CA29" s="34">
-        <f>[1]Annual!Y436</f>
-        <v>5.6399069224808471</v>
+        <v>5.6296193767359597</v>
       </c>
       <c r="CB29" s="34">
-        <f>[1]Annual!Z436</f>
-        <v>1.5239268382415645</v>
+        <v>1.7063448694312484</v>
       </c>
     </row>
     <row r="30" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -25112,104 +22569,79 @@
         <v>3.3480573236572155</v>
       </c>
       <c r="BD30" s="26">
-        <f>[1]Annual!B441</f>
         <v>3.8504730238576883</v>
       </c>
       <c r="BE30" s="26">
-        <f>[1]Annual!C441</f>
         <v>3.771936081718394</v>
       </c>
       <c r="BF30" s="26">
-        <f>[1]Annual!D441</f>
         <v>5.3066814298613991</v>
       </c>
       <c r="BG30" s="26">
-        <f>[1]Annual!E441</f>
         <v>8.2936780316530161</v>
       </c>
       <c r="BH30" s="26">
-        <f>[1]Annual!F441</f>
         <v>5.2819632342929594</v>
       </c>
       <c r="BI30" s="26">
-        <f>[1]Annual!G441</f>
         <v>6.4136363188305126</v>
       </c>
       <c r="BJ30" s="26">
-        <f>[1]Annual!H441</f>
         <v>7.695710341755003</v>
       </c>
       <c r="BK30" s="26">
-        <f>[1]Annual!I441</f>
         <v>3.9886933128141351</v>
       </c>
       <c r="BL30" s="26">
-        <f>[1]Annual!J441</f>
         <v>3.4257677575938175</v>
       </c>
       <c r="BM30" s="26">
-        <f>[1]Annual!K441</f>
         <v>7.553215154649223</v>
       </c>
       <c r="BN30" s="26">
-        <f>[1]Annual!L441</f>
         <v>5.1684657298538923</v>
       </c>
       <c r="BO30" s="26">
-        <f>[1]Annual!M441</f>
         <v>7.3808691902351313</v>
       </c>
       <c r="BP30" s="26">
-        <f>[1]Annual!N441</f>
         <v>7.5711768242778987</v>
       </c>
       <c r="BQ30" s="26">
-        <f>[1]Annual!O441</f>
         <v>6.7174996920232246</v>
       </c>
       <c r="BR30" s="26">
-        <f>[1]Annual!P441</f>
         <v>7.4136407800169764</v>
       </c>
       <c r="BS30" s="26">
-        <f>[1]Annual!Q441</f>
         <v>8.1741539634557085</v>
       </c>
       <c r="BT30" s="26">
-        <f>[1]Annual!R441</f>
         <v>7.3564353009879113</v>
       </c>
       <c r="BU30" s="26">
-        <f>[1]Annual!S441</f>
         <v>6.742605900669929</v>
       </c>
       <c r="BV30" s="26">
-        <f>[1]Annual!T441</f>
         <v>7.2433588277661158</v>
       </c>
       <c r="BW30" s="34">
-        <f>[1]Annual!U441</f>
         <v>-9.1272079402560991</v>
       </c>
       <c r="BX30" s="34">
-        <f>[1]Annual!V441</f>
         <v>5.3665446534042758</v>
       </c>
       <c r="BY30" s="34">
-        <f>[1]Annual!W441</f>
         <v>9.2289937899219012</v>
       </c>
       <c r="BZ30" s="34">
-        <f>[1]Annual!X441</f>
         <v>7.0608205359761627</v>
       </c>
       <c r="CA30" s="34">
-        <f>[1]Annual!Y441</f>
-        <v>6.7057387530641535</v>
+        <v>6.7488219645746454</v>
       </c>
       <c r="CB30" s="34">
-        <f>[1]Annual!Z441</f>
-        <v>5.9030673752943841</v>
+        <v>5.8162379688952512</v>
       </c>
     </row>
     <row r="31" spans="1:81" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -25461,104 +22893,79 @@
         <v>4.3825048335741457</v>
       </c>
       <c r="BD32" s="27">
-        <f>[1]Annual!B454</f>
         <v>3.0492313441098133</v>
       </c>
       <c r="BE32" s="27">
-        <f>[1]Annual!C454</f>
         <v>3.7162550018348526</v>
       </c>
       <c r="BF32" s="27">
-        <f>[1]Annual!D454</f>
         <v>5.0869111341206121</v>
       </c>
       <c r="BG32" s="27">
-        <f>[1]Annual!E454</f>
         <v>6.569228512800791</v>
       </c>
       <c r="BH32" s="27">
-        <f>[1]Annual!F454</f>
         <v>4.9425051178358075</v>
       </c>
       <c r="BI32" s="27">
-        <f>[1]Annual!G454</f>
         <v>5.3164168221744461</v>
       </c>
       <c r="BJ32" s="27">
-        <f>[1]Annual!H454</f>
         <v>6.5192915503707241</v>
       </c>
       <c r="BK32" s="27">
-        <f>[1]Annual!I454</f>
         <v>4.344487304883387</v>
       </c>
       <c r="BL32" s="27">
-        <f>[1]Annual!J454</f>
         <v>1.4483230628297576</v>
       </c>
       <c r="BM32" s="27">
-        <f>[1]Annual!K454</f>
         <v>7.3344999604172898</v>
       </c>
       <c r="BN32" s="27">
-        <f>[1]Annual!L454</f>
         <v>3.8582328274785311</v>
       </c>
       <c r="BO32" s="27">
-        <f>[1]Annual!M454</f>
         <v>6.8969517105742</v>
       </c>
       <c r="BP32" s="27">
-        <f>[1]Annual!N454</f>
         <v>6.7505313017787785</v>
       </c>
       <c r="BQ32" s="27">
-        <f>[1]Annual!O454</f>
         <v>6.3479874825022762</v>
       </c>
       <c r="BR32" s="27">
-        <f>[1]Annual!P454</f>
         <v>6.3483097167204932</v>
       </c>
       <c r="BS32" s="27">
-        <f>[1]Annual!Q454</f>
         <v>7.14945674959813</v>
       </c>
       <c r="BT32" s="27">
-        <f>[1]Annual!R454</f>
         <v>6.9309883258640355</v>
       </c>
       <c r="BU32" s="27">
-        <f>[1]Annual!S454</f>
         <v>6.3414855714878371</v>
       </c>
       <c r="BV32" s="27">
-        <f>[1]Annual!T454</f>
         <v>6.118525662562547</v>
       </c>
       <c r="BW32" s="27">
-        <f>[1]Annual!U454</f>
         <v>-9.518294740699119</v>
       </c>
       <c r="BX32" s="27">
-        <f>[1]Annual!V454</f>
         <v>5.7147331321929471</v>
       </c>
       <c r="BY32" s="27">
-        <f>[1]Annual!W454</f>
         <v>7.5809821277173199</v>
       </c>
       <c r="BZ32" s="27">
-        <f>[1]Annual!X454</f>
         <v>5.5189496785154546</v>
       </c>
       <c r="CA32" s="27">
-        <f>[1]Annual!Y454</f>
-        <v>5.6920161281656618</v>
+        <v>5.7147452612866374</v>
       </c>
       <c r="CB32" s="27">
-        <f>[1]Annual!Z454</f>
-        <v>4.403389306011249</v>
+        <v>4.4024015871060129</v>
       </c>
     </row>
     <row r="33" spans="1:81" x14ac:dyDescent="0.2">
@@ -25978,9 +23385,8 @@
       <c r="CA38" s="19"/>
     </row>
     <row r="39" spans="1:81" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="str">
-        <f>$A$3</f>
-        <v>As of January 2026</v>
+      <c r="A39" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="19"/>
@@ -26896,108 +24302,82 @@
         <v>15.378930289536111</v>
       </c>
       <c r="BD46" s="22">
-        <f>[1]Annual!B281</f>
         <v>15.23187848636881</v>
       </c>
       <c r="BE46" s="22">
-        <f>[1]Annual!C281</f>
         <v>15.352300283778639</v>
       </c>
       <c r="BF46" s="22">
-        <f>[1]Annual!D281</f>
         <v>15.336282442514907</v>
       </c>
       <c r="BG46" s="22">
-        <f>[1]Annual!E281</f>
         <v>15.261537944966964</v>
       </c>
       <c r="BH46" s="22">
-        <f>[1]Annual!F281</f>
         <v>15.035252962513354</v>
       </c>
       <c r="BI46" s="22">
-        <f>[1]Annual!G281</f>
         <v>14.828140996860578</v>
       </c>
       <c r="BJ46" s="22">
-        <f>[1]Annual!H281</f>
         <v>14.724672528670688</v>
       </c>
       <c r="BK46" s="22">
-        <f>[1]Annual!I281</f>
         <v>14.565802703995139</v>
       </c>
       <c r="BL46" s="22">
-        <f>[1]Annual!J281</f>
         <v>14.432571542304128</v>
       </c>
       <c r="BM46" s="22">
-        <f>[1]Annual!K281</f>
         <v>14.205940089151406</v>
       </c>
       <c r="BN46" s="22">
-        <f>[1]Annual!L281</f>
         <v>13.410402455254742</v>
       </c>
       <c r="BO46" s="22">
-        <f>[1]Annual!M281</f>
         <v>13.349178580653176</v>
       </c>
       <c r="BP46" s="22">
-        <f>[1]Annual!N281</f>
         <v>12.872515279882263</v>
       </c>
       <c r="BQ46" s="22">
-        <f>[1]Annual!O281</f>
         <v>12.412191012710249</v>
       </c>
       <c r="BR46" s="22">
-        <f>[1]Annual!P281</f>
         <v>11.889903498085461</v>
       </c>
       <c r="BS46" s="22">
-        <f>[1]Annual!Q281</f>
         <v>11.26245199822255</v>
       </c>
       <c r="BT46" s="22">
-        <f>[1]Annual!R281</f>
         <v>10.409753604042638</v>
       </c>
       <c r="BU46" s="22">
-        <f>[1]Annual!S281</f>
         <v>10.148675582172299</v>
       </c>
       <c r="BV46" s="22">
-        <f>[1]Annual!T281</f>
         <v>9.6501403580565963</v>
       </c>
       <c r="BW46" s="26">
-        <f>[1]Annual!U281</f>
         <v>9.2033126929201572</v>
       </c>
       <c r="BX46" s="26">
-        <f>[1]Annual!V281</f>
         <v>10.151707571626631</v>
       </c>
       <c r="BY46" s="26">
-        <f>[1]Annual!W281</f>
         <v>9.5749851837800009</v>
       </c>
       <c r="BZ46" s="26">
-        <f>[1]Annual!X281</f>
         <v>8.9429961290592548</v>
       </c>
       <c r="CA46" s="26">
-        <f>[1]Annual!Y281</f>
         <v>8.5773215738840456</v>
       </c>
       <c r="CB46" s="26">
-        <f>[1]Annual!Z281</f>
-        <v>7.9940928925913788</v>
+        <v>7.9913162521655927</v>
       </c>
       <c r="CC46" s="26">
-        <f>[1]Annual!AA281</f>
-        <v>7.8932207059278321</v>
+        <v>7.8906408096505576</v>
       </c>
     </row>
     <row r="47" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -27167,108 +24547,82 @@
         <v>31.295988383797184</v>
       </c>
       <c r="BD47" s="22">
-        <f>[1]Annual!B282</f>
         <v>31.971501516512134</v>
       </c>
       <c r="BE47" s="22">
-        <f>[1]Annual!C282</f>
         <v>31.440568627076409</v>
       </c>
       <c r="BF47" s="22">
-        <f>[1]Annual!D282</f>
         <v>31.428021702706282</v>
       </c>
       <c r="BG47" s="22">
-        <f>[1]Annual!E282</f>
         <v>31.39143335684199</v>
       </c>
       <c r="BH47" s="22">
-        <f>[1]Annual!F282</f>
         <v>30.754483620844571</v>
       </c>
       <c r="BI47" s="22">
-        <f>[1]Annual!G282</f>
         <v>30.786241339984993</v>
       </c>
       <c r="BJ47" s="22">
-        <f>[1]Annual!H282</f>
         <v>30.323103367904015</v>
       </c>
       <c r="BK47" s="22">
-        <f>[1]Annual!I282</f>
         <v>29.875070648235653</v>
       </c>
       <c r="BL47" s="22">
-        <f>[1]Annual!J282</f>
         <v>30.197747404768048</v>
       </c>
       <c r="BM47" s="22">
-        <f>[1]Annual!K282</f>
         <v>29.345105403779193</v>
       </c>
       <c r="BN47" s="22">
-        <f>[1]Annual!L282</f>
         <v>30.025617169443773</v>
       </c>
       <c r="BO47" s="22">
-        <f>[1]Annual!M282</f>
         <v>29.373253048569385</v>
       </c>
       <c r="BP47" s="22">
-        <f>[1]Annual!N282</f>
         <v>29.590623487536909</v>
       </c>
       <c r="BQ47" s="22">
-        <f>[1]Annual!O282</f>
         <v>29.608632695726328</v>
       </c>
       <c r="BR47" s="22">
-        <f>[1]Annual!P282</f>
         <v>29.929468221979217</v>
       </c>
       <c r="BS47" s="22">
-        <f>[1]Annual!Q282</f>
         <v>29.974102460770258</v>
       </c>
       <c r="BT47" s="22">
-        <f>[1]Annual!R282</f>
         <v>30.264831240272059</v>
       </c>
       <c r="BU47" s="22">
-        <f>[1]Annual!S282</f>
         <v>30.289870871203394</v>
       </c>
       <c r="BV47" s="22">
-        <f>[1]Annual!T282</f>
         <v>30.563740154978003</v>
       </c>
       <c r="BW47" s="26">
-        <f>[1]Annual!U282</f>
         <v>30.37684802804343</v>
       </c>
       <c r="BX47" s="26">
-        <f>[1]Annual!V282</f>
         <v>29.167301996634841</v>
       </c>
       <c r="BY47" s="26">
-        <f>[1]Annual!W282</f>
         <v>29.943886987581429</v>
       </c>
       <c r="BZ47" s="26">
-        <f>[1]Annual!X282</f>
         <v>29.6493776776883</v>
       </c>
       <c r="CA47" s="26">
-        <f>[1]Annual!Y282</f>
         <v>29.117747724605188</v>
       </c>
       <c r="CB47" s="26">
-        <f>[1]Annual!Z282</f>
-        <v>29.103391836990927</v>
+        <v>29.094300910018873</v>
       </c>
       <c r="CC47" s="26">
-        <f>[1]Annual!AA282</f>
-        <v>28.300715553812211</v>
+        <v>28.342978294618469</v>
       </c>
     </row>
     <row r="48" spans="1:81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -27438,108 +24792,82 @@
         <v>53.325081326666698</v>
       </c>
       <c r="BD48" s="22">
-        <f>[1]Annual!B287</f>
         <v>52.796619997119052</v>
       </c>
       <c r="BE48" s="22">
-        <f>[1]Annual!C287</f>
         <v>53.207131089144951</v>
       </c>
       <c r="BF48" s="22">
-        <f>[1]Annual!D287</f>
         <v>53.235695854778811</v>
       </c>
       <c r="BG48" s="22">
-        <f>[1]Annual!E287</f>
         <v>53.347028698191046</v>
       </c>
       <c r="BH48" s="22">
-        <f>[1]Annual!F287</f>
         <v>54.210263416642071</v>
       </c>
       <c r="BI48" s="22">
-        <f>[1]Annual!G287</f>
         <v>54.385617663154441</v>
       </c>
       <c r="BJ48" s="22">
-        <f>[1]Annual!H287</f>
         <v>54.952224103425308</v>
       </c>
       <c r="BK48" s="22">
-        <f>[1]Annual!I287</f>
         <v>55.559126647769205</v>
       </c>
       <c r="BL48" s="22">
-        <f>[1]Annual!J287</f>
         <v>55.369681052927831</v>
       </c>
       <c r="BM48" s="22">
-        <f>[1]Annual!K287</f>
         <v>56.448954507069402</v>
       </c>
       <c r="BN48" s="22">
-        <f>[1]Annual!L287</f>
         <v>56.56398037530149</v>
       </c>
       <c r="BO48" s="22">
-        <f>[1]Annual!M287</f>
         <v>57.277568370777445</v>
       </c>
       <c r="BP48" s="22">
-        <f>[1]Annual!N287</f>
         <v>57.536861232580819</v>
       </c>
       <c r="BQ48" s="22">
-        <f>[1]Annual!O287</f>
         <v>57.979176291563427</v>
       </c>
       <c r="BR48" s="22">
-        <f>[1]Annual!P287</f>
         <v>58.18062827993532</v>
       </c>
       <c r="BS48" s="22">
-        <f>[1]Annual!Q287</f>
         <v>58.763445541007187</v>
       </c>
       <c r="BT48" s="22">
-        <f>[1]Annual!R287</f>
         <v>59.325415155685299</v>
       </c>
       <c r="BU48" s="22">
-        <f>[1]Annual!S287</f>
         <v>59.561453546624307</v>
       </c>
       <c r="BV48" s="22">
-        <f>[1]Annual!T287</f>
         <v>59.786119486965397</v>
       </c>
       <c r="BW48" s="26">
-        <f>[1]Annual!U287</f>
         <v>60.419839279036417</v>
       </c>
       <c r="BX48" s="26">
-        <f>[1]Annual!V287</f>
         <v>60.680990431738536</v>
       </c>
       <c r="BY48" s="26">
-        <f>[1]Annual!W287</f>
         <v>60.481127828638584</v>
       </c>
       <c r="BZ48" s="26">
-        <f>[1]Annual!X287</f>
         <v>61.407626193252426</v>
       </c>
       <c r="CA48" s="26">
-        <f>[1]Annual!Y287</f>
         <v>62.304930701510763</v>
       </c>
       <c r="CB48" s="26">
-        <f>[1]Annual!Z287</f>
-        <v>62.902515270417695</v>
+        <v>62.914382837815538</v>
       </c>
       <c r="CC48" s="26">
-        <f>[1]Annual!AA287</f>
-        <v>63.806063740259965</v>
+        <v>63.766380895730968</v>
       </c>
     </row>
     <row r="49" spans="1:81" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -27792,107 +25120,81 @@
         <v>100</v>
       </c>
       <c r="BD50" s="32">
-        <f>[1]Annual!B300</f>
         <v>100</v>
       </c>
       <c r="BE50" s="32">
-        <f>[1]Annual!C300</f>
         <v>100</v>
       </c>
       <c r="BF50" s="32">
-        <f>[1]Annual!D300</f>
         <v>100</v>
       </c>
       <c r="BG50" s="32">
-        <f>[1]Annual!E300</f>
         <v>100</v>
       </c>
       <c r="BH50" s="32">
-        <f>[1]Annual!F300</f>
         <v>100</v>
       </c>
       <c r="BI50" s="32">
-        <f>[1]Annual!G300</f>
         <v>100</v>
       </c>
       <c r="BJ50" s="32">
-        <f>[1]Annual!H300</f>
         <v>100</v>
       </c>
       <c r="BK50" s="32">
-        <f>[1]Annual!I300</f>
         <v>100</v>
       </c>
       <c r="BL50" s="32">
-        <f>[1]Annual!J300</f>
         <v>100</v>
       </c>
       <c r="BM50" s="32">
-        <f>[1]Annual!K300</f>
         <v>100</v>
       </c>
       <c r="BN50" s="32">
-        <f>[1]Annual!L300</f>
         <v>100</v>
       </c>
       <c r="BO50" s="32">
-        <f>[1]Annual!M300</f>
         <v>100</v>
       </c>
       <c r="BP50" s="32">
-        <f>[1]Annual!N300</f>
         <v>100</v>
       </c>
       <c r="BQ50" s="32">
-        <f>[1]Annual!O300</f>
         <v>100</v>
       </c>
       <c r="BR50" s="32">
-        <f>[1]Annual!P300</f>
         <v>100</v>
       </c>
       <c r="BS50" s="32">
-        <f>[1]Annual!Q300</f>
         <v>100</v>
       </c>
       <c r="BT50" s="32">
-        <f>[1]Annual!R300</f>
         <v>100</v>
       </c>
       <c r="BU50" s="32">
-        <f>[1]Annual!S300</f>
         <v>100</v>
       </c>
       <c r="BV50" s="32">
-        <f>[1]Annual!T300</f>
         <v>100</v>
       </c>
       <c r="BW50" s="27">
-        <f>[1]Annual!U300</f>
         <v>100</v>
       </c>
       <c r="BX50" s="27">
-        <f>[1]Annual!V300</f>
         <v>100</v>
       </c>
       <c r="BY50" s="27">
-        <f>[1]Annual!W300</f>
         <v>100</v>
       </c>
       <c r="BZ50" s="27">
-        <f>[1]Annual!X300</f>
         <v>100</v>
       </c>
       <c r="CA50" s="27">
-        <f>[1]Annual!Y300</f>
         <v>100</v>
       </c>
       <c r="CB50" s="27">
-        <f>[1]Annual!Z300</f>
         <v>100</v>
       </c>
       <c r="CC50" s="27">
-        <f>[1]Annual!AA300</f>
         <v>100</v>
       </c>
     </row>
